--- a/data/merged/2026-09-28/MERGED_JP_Spot-Cleaner_2026-09-28.xlsx
+++ b/data/merged/2026-09-28/MERGED_JP_Spot-Cleaner_2026-09-28.xlsx
@@ -7500,13 +7500,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7588,13 +7588,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
+      <xdr:rowOff>44999</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>46</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
+      <xdr:rowOff>269999</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7632,13 +7632,13 @@
       <xdr:col>1</xdr:col>
       <xdr:colOff>192000</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
+      <xdr:rowOff>45000</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>1</xdr:col>
       <xdr:colOff>428799</xdr:colOff>
       <xdr:row>47</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
+      <xdr:rowOff>270000</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -7699,94 +7699,6 @@
       </xdr:nvPicPr>
       <xdr:blipFill>
         <a:blip r:embed="rId48" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>45000</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>270000</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="49" name="Product 49">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId49" cstate="print"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="0"/>
-          <a:ext cx="0" cy="0"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>192000</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>44999</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>428799</xdr:colOff>
-      <xdr:row>50</xdr:row>
-      <xdr:rowOff>269999</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="50" name="Product 50">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <ns2:creationId id="{00000000-0008-0000-0000-000002000000}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip r:embed="rId50" cstate="print"/>
         <a:stretch>
           <a:fillRect/>
         </a:stretch>
@@ -8128,7 +8040,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:BR51"/>
+  <dimension ref="A1:BR49"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="5" style="1" customWidth="1"/>
@@ -17088,271 +17000,31 @@
       <c r="B37" s="11"/>
       <c r="C37" s="12" t="inlineStr">
         <is>
-          <t>B0H8SPVHVZ</t>
-        </is>
-      </c>
-      <c r="D37" s="12" t="inlineStr">
-        <is>
-          <t>颜色: ゴールド</t>
-        </is>
-      </c>
+          <t>B005MWZKNI</t>
+        </is>
+      </c>
+      <c r="D37" s="12"/>
       <c r="E37" s="12" t="inlineStr">
         <is>
-          <t>品牌: evove | 特殊功能: 急速加熱 | 推荐表面: キッチン、浴室、トイレ、窓、タイル、カーテン | 随附部件: ノズル | 油箱容积: 1250 毫升</t>
+          <t>品牌: Iris Ohyama | 特殊功能: 儿童锁 | 推荐表面: 家具装饰品 | 型号名称: 便携型 12件套 除菌 除臭 轻量 白色 | 随附部件: 直喷嘴、灵活喷嘴、布用喷嘴、角度喷嘴、喷嘴盖、点刷、</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
         <is>
-          <t>evove</t>
+          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/%E3%81%8D%E3%82%8C%E3%81%84%E3%81%AE%E6%99%82%E9%96%93%E3%82%92%E3%80%81%E7%A7%81%E3%81%AE%E6%99%82%E9%96%93%E3%81%AB%E3%80%82/page/B441CACF-20A2-4071-9530-2CC8DA3A24B6?lp_asin=B0H8SPVHVZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B005MWZKNI&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>【12秒速熱・大容量タンク】evove スチームクリーナー 120℃高温 高圧 ハンディタイプ 1500W 除菌率99.9% 水タンク1250ml 8種ノズル付き 油汚れ ペット 赤ちゃん おもちゃ 年末清掃 SC01</t>
+          <t>爱丽思欧雅玛 蒸汽清洁器 手持型 白色 STM-303</t>
         </is>
       </c>
       <c r="I37" s="12" t="inlineStr">
-        <is>
-          <t>【業界トップクラスの速熱性と強力な洗浄力】12秒で噴射開始、4.5BARの圧力で頑固な油汚れも瞬時に分解。1500Wの高出力ヒーターを搭載し、電源オンからわずか12秒で高温スチームを噴射します。待ち時間ゼロの「即熱式」なので、思い立った時にすぐ掃除が可能です。蒸気温度は約120℃、圧力4.5BARの強力な噴射力で、キッチン周りのこびりついた油汚れや浴室の黒ずみを化学洗剤なしで根こそぎ落とします。従来の沸騰式と違い、加熱・冷却の待ち時間が不要なため、ストレスなく快適に清掃を進められます。
-【赤ちゃんやペットにも安心な「化学洗剤不使用」の衛生環境】除.菌率99.9%、水だけで徹底消毒できる安全設計。 高温スチームの力で雑菌やダニを99.9%除菌。洗剤や薬品を一切使用しないため、舐めても安心な赤ちゃんのおもちゃ、ペットの寝床、食器棚などの清潔維持に最適です。本体は「給湯器式」の即時加熱システムを採用しており、従来型の「圧力鍋式（沸騰式）」製品のように内部に高圧が溜まり続けることがないため、爆発のリスクがなく極めて安全。お子様やペットがいるご家庭でも、安心してご利用いただけます。
-【片手で楽々操作、1250ml大容量タンクで長時間連続使用】本体を持ち歩く従来の製品とは異なり、軽量なハンドル部分だけで操作できるため、腕への負担が激減します。女性や高齢者でも無理なく掃除が可能。1250mlの大型透明タンクを搭載し、満水時なら最強モードでも約35分連続噴射できます。広い窓幅の注ぎ口で給水も簡単、底部の排水口を使えば使用后の水抜きもスムーズ。コード長1.41m、ホース長2mで広範囲をカバーし、収納時も場所を取りません。
-【直感的なタッチパネルと6段階スチーム調整機能】用途に合わせて噴射量を微調整、操作性と耐久性を両立。見やすいタッチパネル式の操作盤で、＋/－ボタンによりスチーム量を6段階で細かく調整可能。delicateな素材から頑固な汚れまで、場面に応じて最適な洗浄力を選べます。耐久性を最優先し、高温による故障を防ぐためハンドル部にスイッチを設けない堅牢な設計を採用しています（※使用中はホースが熱くなるため、直接触れないようご注意ください）。付属の耐熱手袋を着用すれば、より安全に作業を行えます。
-【8種類のアタッチメントで家中の隅々まで対応】専用ブラシで隙間も完璧清掃、取り付けの注意点付き。多様な清掃シーンに対応する8種類の専用ノズルが付属。高圧ノズル、窓用スクレーパー、真鍮・ナイロンブラシ、大小シャベルなど、換気扇のフィルターからタイルの目地、カーテンの消臭までこれ1台で完結します。※※※ブラシ装着時は確実にねじ込んで固定してください（外れる恐れがあります）。また、金属製ブラシは白いタイルに色移りする可能性があるため、使用箇所にご注意ください。</t>
-        </is>
-      </c>
-      <c r="J37" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H8SPVHVZ?psc=1</t>
-        </is>
-      </c>
-      <c r="K37" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/418sjd-uV7L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L37" s="12" t="inlineStr">
-        <is>
-          <t>B0GLQ3BZZT</t>
-        </is>
-      </c>
-      <c r="M37" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:清洁机</t>
-        </is>
-      </c>
-      <c r="N37" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O37" s="13">
-        <v>44711</v>
-      </c>
-      <c r="P37" s="13">
-        <v>-18970</v>
-      </c>
-      <c r="Q37" s="14">
-        <v>-0.61</v>
-      </c>
-      <c r="R37" s="15" t="inlineStr">
-        <is>
-          <t>电动清洗机\\\\清洁机</t>
-        </is>
-      </c>
-      <c r="S37" s="16" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="T37" s="13">
-        <v>70</v>
-      </c>
-      <c r="U37" s="14">
-        <v>-0.03</v>
-      </c>
-      <c r="V37" s="13">
-        <v>559930</v>
-      </c>
-      <c r="W37" s="13"/>
-      <c r="X37" s="13"/>
-      <c r="Y37" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z37" s="13">
-        <v>7999</v>
-      </c>
-      <c r="AA37" s="2"/>
-      <c r="AB37" s="1"/>
-      <c r="AC37" s="2"/>
-      <c r="AD37" s="17">
-        <v>20</v>
-      </c>
-      <c r="AE37" s="13">
-        <v>0</v>
-      </c>
-      <c r="AF37" s="18">
-        <v>4.4</v>
-      </c>
-      <c r="AG37" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH37" s="13">
-        <v>472</v>
-      </c>
-      <c r="AI37" s="14">
-        <v>0.78</v>
-      </c>
-      <c r="AJ37"/>
-      <c r="AK37" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="AL37" s="17">
-        <v>27</v>
-      </c>
-      <c r="AM37" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN37" s="11"/>
-      <c r="AO37" s="11"/>
-      <c r="AP37" s="2"/>
-      <c r="AQ37" s="17">
-        <v>10</v>
-      </c>
-      <c r="AR37" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS37" s="12" t="inlineStr">
-        <is>
-          <t>EVOVE</t>
-        </is>
-      </c>
-      <c r="AT37" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU37" s="11" t="inlineStr">
-        <is>
-          <t>CN(HK)</t>
-        </is>
-      </c>
-      <c r="AV37" s="12" t="inlineStr">
-        <is>
-          <t>紅磡 九龍 999077 HK</t>
-        </is>
-      </c>
-      <c r="AW37" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3WKMH8N8T04I</t>
-        </is>
-      </c>
-      <c r="AX37" s="11"/>
-      <c r="AY37" s="11"/>
-      <c r="AZ37" s="11"/>
-      <c r="BA37" s="11"/>
-      <c r="BB37" s="11"/>
-      <c r="BC37" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD37" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE37" s="11"/>
-      <c r="BF37" s="11"/>
-      <c r="BG37" s="11"/>
-      <c r="BH37" s="12"/>
-      <c r="BI37" s="20"/>
-      <c r="BJ37" s="20" t="inlineStr">
-        <is>
-          <t>1.97 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK37" s="20" t="inlineStr">
-        <is>
-          <t>1.97 kg</t>
-        </is>
-      </c>
-      <c r="BL37" s="20" t="inlineStr">
-        <is>
-          <t>17.3 x 13.5 x 21.5 cm</t>
-        </is>
-      </c>
-      <c r="BM37" s="20" t="inlineStr">
-        <is>
-          <t>17.30 x 13.50 x 21.50 cm</t>
-        </is>
-      </c>
-      <c r="BN37" s="20" t="inlineStr">
-        <is>
-          <t>1.97 kg</t>
-        </is>
-      </c>
-      <c r="BO37" s="20" t="inlineStr">
-        <is>
-          <t>1.97 kg</t>
-        </is>
-      </c>
-      <c r="BP37" s="20" t="inlineStr">
-        <is>
-          <t>28.4 x 21.8 x 17.9 cm</t>
-        </is>
-      </c>
-      <c r="BQ37" s="20" t="inlineStr">
-        <is>
-          <t>28.40 x 21.80 x 17.90 cm</t>
-        </is>
-      </c>
-      <c r="BR37" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="11">
-        <v>37</v>
-      </c>
-      <c r="B38" s="11"/>
-      <c r="C38" s="12" t="inlineStr">
-        <is>
-          <t>B005MWZKNI</t>
-        </is>
-      </c>
-      <c r="D38" s="12"/>
-      <c r="E38" s="12" t="inlineStr">
-        <is>
-          <t>品牌: Iris Ohyama | 特殊功能: 儿童锁 | 推荐表面: 家具装饰品 | 型号名称: 便携型 12件套 除菌 除臭 轻量 白色 | 随附部件: 直喷嘴、灵活喷嘴、布用喷嘴、角度喷嘴、喷嘴盖、点刷、</t>
-        </is>
-      </c>
-      <c r="F38" s="12" t="inlineStr">
-        <is>
-          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
-        </is>
-      </c>
-      <c r="G38" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B005MWZKNI&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H38" s="12" t="inlineStr">
-        <is>
-          <t>爱丽思欧雅玛 蒸汽清洁器 手持型 白色 STM-303</t>
-        </is>
-      </c>
-      <c r="I38" s="12" t="inlineStr">
         <is>
           <t>电源:AC100V
 耗电量:1000W
@@ -17364,19 +17036,261 @@
 套装内容:主体、紧凑喷嘴、直喷嘴、角度喷嘴、漏斗、点刷(3个)、量杯、灵活喷嘴、布罩(2个)</t>
         </is>
       </c>
+      <c r="J37" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B005MWZKNI?psc=1</t>
+        </is>
+      </c>
+      <c r="K37" s="12" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41ag3BndzyL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L37" s="12" t="inlineStr">
+        <is>
+          <t>B005MWZKNI</t>
+        </is>
+      </c>
+      <c r="M37" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装:消费性电子产品:电器:清洁机</t>
+        </is>
+      </c>
+      <c r="N37" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装</t>
+        </is>
+      </c>
+      <c r="O37" s="13">
+        <v>54529</v>
+      </c>
+      <c r="P37" s="13">
+        <v>19755</v>
+      </c>
+      <c r="Q37" s="14">
+        <v>0.5</v>
+      </c>
+      <c r="R37" s="15" t="inlineStr">
+        <is>
+          <t>电动清洗机\\\\清洁机</t>
+        </is>
+      </c>
+      <c r="S37" s="16" t="inlineStr">
+        <is>
+          <t>37</t>
+        </is>
+      </c>
+      <c r="T37" s="13">
+        <v>107</v>
+      </c>
+      <c r="U37" s="14">
+        <v>1.13</v>
+      </c>
+      <c r="V37" s="13">
+        <v>513600</v>
+      </c>
+      <c r="W37" s="13" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="X37" s="13">
+        <v>311231</v>
+      </c>
+      <c r="Y37" s="17">
+        <v>1</v>
+      </c>
+      <c r="Z37" s="13">
+        <v>4800</v>
+      </c>
+      <c r="AA37" s="2"/>
+      <c r="AB37" s="1"/>
+      <c r="AC37" s="2"/>
+      <c r="AD37" s="17">
+        <v>933</v>
+      </c>
+      <c r="AE37" s="13">
+        <v>0</v>
+      </c>
+      <c r="AF37" s="18">
+        <v>3.6</v>
+      </c>
+      <c r="AG37" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH37" s="13">
+        <v>472</v>
+      </c>
+      <c r="AI37" s="14">
+        <v>0.77</v>
+      </c>
+      <c r="AJ37"/>
+      <c r="AK37" s="11" t="inlineStr">
+        <is>
+          <t>2012-06-15</t>
+        </is>
+      </c>
+      <c r="AL37" s="17">
+        <v>5218</v>
+      </c>
+      <c r="AM37" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN37" s="11"/>
+      <c r="AO37" s="11"/>
+      <c r="AP37" s="2"/>
+      <c r="AQ37" s="17">
+        <v>8</v>
+      </c>
+      <c r="AR37" s="17">
+        <v>35</v>
+      </c>
+      <c r="AS37" s="12" t="inlineStr">
+        <is>
+          <t>Amazon</t>
+        </is>
+      </c>
+      <c r="AT37" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU37" s="11" t="inlineStr">
+        <is>
+          <t>JP</t>
+        </is>
+      </c>
+      <c r="AV37" s="12" t="inlineStr">
+        <is>
+          <t>大田区 東京都 1430016 JP</t>
+        </is>
+      </c>
+      <c r="AW37" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=APF7PXDXK20CB</t>
+        </is>
+      </c>
+      <c r="AX37" s="11"/>
+      <c r="AY37" s="11"/>
+      <c r="AZ37" s="11"/>
+      <c r="BA37" s="11"/>
+      <c r="BB37" s="11"/>
+      <c r="BC37" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD37" s="11"/>
+      <c r="BE37" s="11"/>
+      <c r="BF37" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG37" s="11"/>
+      <c r="BH37" s="12"/>
+      <c r="BI37" s="20"/>
+      <c r="BJ37" s="20" t="inlineStr">
+        <is>
+          <t>1.8 千克</t>
+        </is>
+      </c>
+      <c r="BK37" s="20"/>
+      <c r="BL37" s="20" t="inlineStr">
+        <is>
+          <t>31 x 13 x 24 cm</t>
+        </is>
+      </c>
+      <c r="BM37" s="20" t="inlineStr">
+        <is>
+          <t>31.00 x 13.00 x 24.00 cm</t>
+        </is>
+      </c>
+      <c r="BN37" s="20" t="inlineStr">
+        <is>
+          <t>2.67 kg</t>
+        </is>
+      </c>
+      <c r="BO37" s="20" t="inlineStr">
+        <is>
+          <t>2.67 kg</t>
+        </is>
+      </c>
+      <c r="BP37" s="20" t="inlineStr">
+        <is>
+          <t>29.8 x 26.2 x 19.2 cm</t>
+        </is>
+      </c>
+      <c r="BQ37" s="20" t="inlineStr">
+        <is>
+          <t>29.80 x 26.20 x 19.20 cm</t>
+        </is>
+      </c>
+      <c r="BR37" s="11" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A38" s="11">
+        <v>37</v>
+      </c>
+      <c r="B38" s="11"/>
+      <c r="C38" s="12" t="inlineStr">
+        <is>
+          <t>B0H74P4ZMB</t>
+        </is>
+      </c>
+      <c r="D38" s="12" t="inlineStr">
+        <is>
+          <t>Set name: 1年メーカー保証</t>
+        </is>
+      </c>
+      <c r="E38" s="12" t="inlineStr">
+        <is>
+          <t>品牌: Yadea | 颜色: 黑色 | 电源: 有线电动 | 制造商: Ningbo Dwafer Electrical Appliances Co.,Ltd. | 商品数量: 1</t>
+        </is>
+      </c>
+      <c r="F38" s="12" t="inlineStr">
+        <is>
+          <t>Yadea</t>
+        </is>
+      </c>
+      <c r="G38" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/-/zh/stores/Yadea/page/DE8B12B7-0E18-4304-A0FC-F26833052784?lp_asin=B0H74P4ZMB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+        </is>
+      </c>
+      <c r="H38" s="12" t="inlineStr">
+        <is>
+          <t>Yadea R3 ultra 地毯清洗机</t>
+        </is>
+      </c>
+      <c r="I38" s="12" t="inlineStr">
+        <is>
+          <t>【史上最小的车身× 最大容量的水箱】Yadea R3 ultra 地毯清洁机新登场！相比旧款R3，车身缩小了30%，占用空间更小。此外，水箱容量提高了7%，虽然紧凑但一次注水即可清洁大范围。（清水箱容量：1450毫升/污水箱容量：1600毫升）
+【"洗不干净的东西"才是R3 ultra的真本事】沙发、地毯、床垫——无法在洗衣机中清洗的大件物品，都可以交给R3 ultra来处理！只需喷水→刷洗→强力吸尘的简单3个步骤，即使是你放弃过的污渍也能干净。■适用范围：床垫、布艺沙发、布艺椅、地毯、地毯、地垫、地垫、窗帘、车内座椅、布艺床垫、毛绒玩具、宠物座垫等。■可处理的污渍类型：长期积累在沙发或地毯上的灰尘/汗渍、咖啡/酱油/油渍、儿童吃剩的食物、宠物的呕吐物/漏粪/爪印等。
+【以18000Pa的力，将渗透的污垢清除至零】超越以往型号，搭载500W高输出电机！18KPa的强力吸引，不仅清洁表面，还能彻底清洁沙发海绵深处渗透的汗渍，以及床垫内残留的宠物尿臭。*推荐的清洁用品：碱性电解水、小苏打、柠檬酸
+[为什么易于维护,但可以继续使用] 水箱和污水箱的全开口规格。 开口较宽,因此即使加水或污水丢弃也很轻松。 因为手伸到深处,所以没有清洗残留,打开盖子直接放置即可自然干燥。 供水、排水、内部清洗、干燥——消除清洁布制品的压力。
+【多样配件供应！使用更方便】■多功能刷头：适用于各种场景，适用范围广泛，能够处理各种布质产品。■大型刷头：能够更轻松地清洁面积大的布质产品（如地毯和床垫等）。■自清洁刷头：能够彻底清洁软管背面的刷头。</t>
+        </is>
+      </c>
       <c r="J38" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B005MWZKNI?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H74P4ZMB?psc=1</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41ag3BndzyL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/71INq-jTsbL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L38" s="12" t="inlineStr">
         <is>
-          <t>B005MWZKNI</t>
+          <t>B0HHHTZ3LQ</t>
         </is>
       </c>
       <c r="M38" s="12" t="inlineStr">
@@ -17390,13 +17304,13 @@
         </is>
       </c>
       <c r="O38" s="13">
-        <v>54529</v>
+        <v>57012</v>
       </c>
       <c r="P38" s="13">
-        <v>19755</v>
+        <v>-83232</v>
       </c>
       <c r="Q38" s="14">
-        <v>0.5</v>
+        <v>-1.9</v>
       </c>
       <c r="R38" s="15" t="inlineStr">
         <is>
@@ -17405,61 +17319,53 @@
       </c>
       <c r="S38" s="16" t="inlineStr">
         <is>
-          <t>37</t>
+          <t>40</t>
         </is>
       </c>
       <c r="T38" s="13">
-        <v>107</v>
-      </c>
-      <c r="U38" s="14">
-        <v>1.13</v>
-      </c>
+        <v>41</v>
+      </c>
+      <c r="U38" s="14"/>
       <c r="V38" s="13">
-        <v>513600</v>
-      </c>
-      <c r="W38" s="13" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="X38" s="13">
-        <v>311231</v>
-      </c>
+        <v>450180</v>
+      </c>
+      <c r="W38" s="13"/>
+      <c r="X38" s="13"/>
       <c r="Y38" s="17">
         <v>1</v>
       </c>
       <c r="Z38" s="13">
-        <v>4800</v>
+        <v>10980</v>
       </c>
       <c r="AA38" s="2"/>
       <c r="AB38" s="1"/>
       <c r="AC38" s="2"/>
       <c r="AD38" s="17">
-        <v>933</v>
+        <v>3</v>
       </c>
       <c r="AE38" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF38" s="18">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="AG38" s="19">
-        <v>0</v>
+        <v>0.024399999999999998</v>
       </c>
       <c r="AH38" s="13">
-        <v>472</v>
+        <v>532</v>
       </c>
       <c r="AI38" s="14">
-        <v>0.77</v>
+        <v>0.8</v>
       </c>
       <c r="AJ38"/>
       <c r="AK38" s="11" t="inlineStr">
         <is>
-          <t>2012-06-15</t>
+          <t>2026-07-12</t>
         </is>
       </c>
       <c r="AL38" s="17">
-        <v>5218</v>
+        <v>77</v>
       </c>
       <c r="AM38" s="11" t="inlineStr">
         <is>
@@ -17473,11 +17379,11 @@
         <v>8</v>
       </c>
       <c r="AR38" s="17">
-        <v>35</v>
+        <v>1</v>
       </c>
       <c r="AS38" s="12" t="inlineStr">
         <is>
-          <t>Amazon</t>
+          <t>株式会社ISANAVI</t>
         </is>
       </c>
       <c r="AT38" s="11" t="inlineStr">
@@ -17492,12 +17398,12 @@
       </c>
       <c r="AV38" s="12" t="inlineStr">
         <is>
-          <t>大田区 東京都 1430016 JP</t>
+          <t>兵庫県 6512116 JP</t>
         </is>
       </c>
       <c r="AW38" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=APF7PXDXK20CB</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FFZRDLOQM7BY</t>
         </is>
       </c>
       <c r="AX38" s="11"/>
@@ -17510,7 +17416,11 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD38" s="11"/>
+      <c r="BD38" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BE38" s="11"/>
       <c r="BF38" s="11" t="inlineStr">
         <is>
@@ -17522,38 +17432,34 @@
       <c r="BI38" s="20"/>
       <c r="BJ38" s="20" t="inlineStr">
         <is>
-          <t>1.8 千克</t>
-        </is>
-      </c>
-      <c r="BK38" s="20"/>
-      <c r="BL38" s="20" t="inlineStr">
-        <is>
-          <t>31 x 13 x 24 cm</t>
-        </is>
-      </c>
-      <c r="BM38" s="20" t="inlineStr">
-        <is>
-          <t>31.00 x 13.00 x 24.00 cm</t>
-        </is>
-      </c>
+          <t>4.28 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK38" s="20" t="inlineStr">
+        <is>
+          <t>4.28 kg</t>
+        </is>
+      </c>
+      <c r="BL38" s="20"/>
+      <c r="BM38" s="20"/>
       <c r="BN38" s="20" t="inlineStr">
         <is>
-          <t>2.67 kg</t>
+          <t>4.28 kg</t>
         </is>
       </c>
       <c r="BO38" s="20" t="inlineStr">
         <is>
-          <t>2.67 kg</t>
+          <t>4.28 kg</t>
         </is>
       </c>
       <c r="BP38" s="20" t="inlineStr">
         <is>
-          <t>29.8 x 26.2 x 19.2 cm</t>
+          <t>41.6 x 33.9 x 19.5 cm</t>
         </is>
       </c>
       <c r="BQ38" s="20" t="inlineStr">
         <is>
-          <t>29.80 x 26.20 x 19.20 cm</t>
+          <t>41.60 x 33.90 x 19.50 cm</t>
         </is>
       </c>
       <c r="BR38" s="11" t="inlineStr">
@@ -17569,56 +17475,48 @@
       <c r="B39" s="11"/>
       <c r="C39" s="12" t="inlineStr">
         <is>
-          <t>B0H74P4ZMB</t>
-        </is>
-      </c>
-      <c r="D39" s="12" t="inlineStr">
-        <is>
-          <t>Set name: 1年メーカー保証</t>
-        </is>
-      </c>
-      <c r="E39" s="12" t="inlineStr">
-        <is>
-          <t>品牌: Yadea | 颜色: 黑色 | 电源: 有线电动 | 制造商: Ningbo Dwafer Electrical Appliances Co.,Ltd. | 商品数量: 1</t>
-        </is>
-      </c>
+          <t>B0BL6RYNQ2</t>
+        </is>
+      </c>
+      <c r="D39" s="12"/>
+      <c r="E39" s="12"/>
       <c r="F39" s="12" t="inlineStr">
         <is>
-          <t>Yadea</t>
+          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/Yadea/page/DE8B12B7-0E18-4304-A0FC-F26833052784?lp_asin=B0H74P4ZMB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0BL6RYNQ2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
         </is>
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>Yadea R3 ultra 地毯清洗机</t>
+          <t>IRIS OHYAMA(IRIS OHYAMA) RNSK-B400D 充电式无线淋水器清洁剂 附带2个电池</t>
         </is>
       </c>
       <c r="I39" s="12" t="inlineStr">
         <is>
-          <t>【史上最小的车身× 最大容量的水箱】Yadea R3 ultra 地毯清洁机新登场！相比旧款R3，车身缩小了30%，占用空间更小。此外，水箱容量提高了7%，虽然紧凑但一次注水即可清洁大范围。（清水箱容量：1450毫升/污水箱容量：1600毫升）
-【"洗不干净的东西"才是R3 ultra的真本事】沙发、地毯、床垫——无法在洗衣机中清洗的大件物品，都可以交给R3 ultra来处理！只需喷水→刷洗→强力吸尘的简单3个步骤，即使是你放弃过的污渍也能干净。■适用范围：床垫、布艺沙发、布艺椅、地毯、地毯、地垫、地垫、窗帘、车内座椅、布艺床垫、毛绒玩具、宠物座垫等。■可处理的污渍类型：长期积累在沙发或地毯上的灰尘/汗渍、咖啡/酱油/油渍、儿童吃剩的食物、宠物的呕吐物/漏粪/爪印等。
-【以18000Pa的力，将渗透的污垢清除至零】超越以往型号，搭载500W高输出电机！18KPa的强力吸引，不仅清洁表面，还能彻底清洁沙发海绵深处渗透的汗渍，以及床垫内残留的宠物尿臭。*推荐的清洁用品：碱性电解水、小苏打、柠檬酸
-[为什么易于维护,但可以继续使用] 水箱和污水箱的全开口规格。 开口较宽,因此即使加水或污水丢弃也很轻松。 因为手伸到深处,所以没有清洗残留,打开盖子直接放置即可自然干燥。 供水、排水、内部清洗、干燥——消除清洁布制品的压力。
-【多样配件供应！使用更方便】■多功能刷头：适用于各种场景，适用范围广泛，能够处理各种布质产品。■大型刷头：能够更轻松地清洁面积大的布质产品（如地毯和床垫等）。■自清洁刷头：能够彻底清洁软管背面的刷头。</t>
+          <t>充电温度:5~35℃ 连续使用时间 ※1:约10分钟●电池:2次锂离子电池●电池容量:1900mAh●电池寿命:重复充电约1000次
+额定电压:DC 10.8V●充电电源(充电适配器)/输入:AC100-240V、50/60Hz/输出:DC 13.7V、0.5A●充电时间:约4小时(根据室温·使用时间等可能延长充电时间。 )
+吸尘功率:约20W。回收罐有效容量:0.4L(根据使用条件而变动。 )●清水罐容量:0.4L●真空软管长度:Φ19mm(内径)×960mm
+热水使用温度:约40℃。商品尺寸(cm):宽约23.3×深约21.3×高约27.7(主体尺寸) 商品质量:2.4kg(包括软管、手提工具)
+配件:手持工具、真空软管、清洁刷、电池×2、充电适配器 ※1 充满电、电池初期温度:20℃</t>
         </is>
       </c>
       <c r="J39" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0H74P4ZMB?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0BL6RYNQ2?psc=1</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
         <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/71INq-jTsbL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31i885y+FLL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L39" s="12" t="inlineStr">
         <is>
-          <t>B0HHHTZ3LQ</t>
+          <t>B0BL6RYNQ2</t>
         </is>
       </c>
       <c r="M39" s="12" t="inlineStr">
@@ -17632,13 +17530,13 @@
         </is>
       </c>
       <c r="O39" s="13">
-        <v>57012</v>
+        <v>49708</v>
       </c>
       <c r="P39" s="13">
-        <v>-83232</v>
+        <v>63857</v>
       </c>
       <c r="Q39" s="14">
-        <v>-1.9</v>
+        <v>0.39</v>
       </c>
       <c r="R39" s="15" t="inlineStr">
         <is>
@@ -17647,15 +17545,17 @@
       </c>
       <c r="S39" s="16" t="inlineStr">
         <is>
-          <t>40</t>
+          <t>35</t>
         </is>
       </c>
       <c r="T39" s="13">
-        <v>41</v>
-      </c>
-      <c r="U39" s="14"/>
+        <v>28</v>
+      </c>
+      <c r="U39" s="14">
+        <v>-0.18</v>
+      </c>
       <c r="V39" s="13">
-        <v>450180</v>
+        <v>436800</v>
       </c>
       <c r="W39" s="13"/>
       <c r="X39" s="13"/>
@@ -17663,37 +17563,37 @@
         <v>1</v>
       </c>
       <c r="Z39" s="13">
-        <v>10980</v>
+        <v>15600</v>
       </c>
       <c r="AA39" s="2"/>
       <c r="AB39" s="1"/>
       <c r="AC39" s="2"/>
       <c r="AD39" s="17">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE39" s="13">
         <v>1</v>
       </c>
       <c r="AF39" s="18">
-        <v>5</v>
+        <v>3.5</v>
       </c>
       <c r="AG39" s="19">
-        <v>0.024399999999999998</v>
+        <v>0.035699999999999996</v>
       </c>
       <c r="AH39" s="13">
-        <v>532</v>
+        <v>675</v>
       </c>
       <c r="AI39" s="14">
-        <v>0.8</v>
+        <v>0.81</v>
       </c>
       <c r="AJ39"/>
       <c r="AK39" s="11" t="inlineStr">
         <is>
-          <t>2026-07-12</t>
+          <t>2022-11-18</t>
         </is>
       </c>
       <c r="AL39" s="17">
-        <v>77</v>
+        <v>1410</v>
       </c>
       <c r="AM39" s="11" t="inlineStr">
         <is>
@@ -17704,14 +17604,14 @@
       <c r="AO39" s="11"/>
       <c r="AP39" s="2"/>
       <c r="AQ39" s="17">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AR39" s="17">
-        <v>1</v>
+        <v>14</v>
       </c>
       <c r="AS39" s="12" t="inlineStr">
         <is>
-          <t>株式会社ISANAVI</t>
+          <t>KUMAMON</t>
         </is>
       </c>
       <c r="AT39" s="11" t="inlineStr">
@@ -17726,12 +17626,12 @@
       </c>
       <c r="AV39" s="12" t="inlineStr">
         <is>
-          <t>兵庫県 6512116 JP</t>
+          <t>熊本県熊 8618039 JP</t>
         </is>
       </c>
       <c r="AW39" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FFZRDLOQM7BY</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2GDOHXNU39HXM</t>
         </is>
       </c>
       <c r="AX39" s="11"/>
@@ -17739,60 +17639,56 @@
       <c r="AZ39" s="11"/>
       <c r="BA39" s="11"/>
       <c r="BB39" s="11"/>
-      <c r="BC39" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD39" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC39" s="11"/>
+      <c r="BD39" s="11"/>
       <c r="BE39" s="11"/>
-      <c r="BF39" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF39" s="11"/>
       <c r="BG39" s="11"/>
       <c r="BH39" s="12"/>
       <c r="BI39" s="20"/>
       <c r="BJ39" s="20" t="inlineStr">
         <is>
-          <t>4.28 Kilograms</t>
+          <t>3.54 Kilograms</t>
         </is>
       </c>
       <c r="BK39" s="20" t="inlineStr">
         <is>
-          <t>4.28 kg</t>
-        </is>
-      </c>
-      <c r="BL39" s="20"/>
-      <c r="BM39" s="20"/>
+          <t>3.54 kg</t>
+        </is>
+      </c>
+      <c r="BL39" s="20" t="inlineStr">
+        <is>
+          <t>39.4 x 28 x 26.8 cm</t>
+        </is>
+      </c>
+      <c r="BM39" s="20" t="inlineStr">
+        <is>
+          <t>39.40 x 28.00 x 26.80 cm</t>
+        </is>
+      </c>
       <c r="BN39" s="20" t="inlineStr">
         <is>
-          <t>4.28 kg</t>
+          <t>3.54 kg</t>
         </is>
       </c>
       <c r="BO39" s="20" t="inlineStr">
         <is>
-          <t>4.28 kg</t>
+          <t>3.54 kg</t>
         </is>
       </c>
       <c r="BP39" s="20" t="inlineStr">
         <is>
-          <t>41.6 x 33.9 x 19.5 cm</t>
+          <t>39.4 x 28 x 26.8 cm</t>
         </is>
       </c>
       <c r="BQ39" s="20" t="inlineStr">
         <is>
-          <t>41.60 x 33.90 x 19.50 cm</t>
+          <t>39.40 x 28.00 x 26.80 cm</t>
         </is>
       </c>
       <c r="BR39" s="11" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>大件</t>
         </is>
       </c>
     </row>
@@ -17803,48 +17699,53 @@
       <c r="B40" s="11"/>
       <c r="C40" s="12" t="inlineStr">
         <is>
-          <t>B0BL6RYNQ2</t>
+          <t>B0H89ZR9LV</t>
         </is>
       </c>
       <c r="D40" s="12"/>
-      <c r="E40" s="12"/>
+      <c r="E40" s="12" t="inlineStr">
+        <is>
+          <t>品牌: GOBOT | 型号名称: GBT-G005 | 随附部件: 蒸汽头附件 | 外型规格: 拖把 | 加热时间: 20 秒</t>
+        </is>
+      </c>
       <c r="F40" s="12" t="inlineStr">
         <is>
-          <t>アイリスオーヤマ(IRIS OHYAMA)</t>
+          <t>GOBOT</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0BL6RYNQ2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/GOBOT/b/ref=bl_dp_s_web_7090029051?ie=UTF8&amp;node=7090029051&amp;field-lbr_brands_browse-bin=GOBOT</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>IRIS OHYAMA(IRIS OHYAMA) RNSK-B400D 充电式无线淋水器清洁剂 附带2个电池</t>
+          <t>GOBOT 蒸汽清洁器 20秒待机 蒸汽拖把 可调节蒸汽量 轻量 地板清洁 高温蒸汽 清洁 水擦拭 蒸汽吸尘器 厨房清洁</t>
         </is>
       </c>
       <c r="I40" s="12" t="inlineStr">
         <is>
-          <t>充电温度:5~35℃ 连续使用时间 ※1:约10分钟●电池:2次锂离子电池●电池容量:1900mAh●电池寿命:重复充电约1000次
-额定电压:DC 10.8V●充电电源(充电适配器)/输入:AC100-240V、50/60Hz/输出:DC 13.7V、0.5A●充电时间:约4小时(根据室温·使用时间等可能延长充电时间。 )
-吸尘功率:约20W。回收罐有效容量:0.4L(根据使用条件而变动。 )●清水罐容量:0.4L●真空软管长度:Φ19mm(内径)×960mm
-热水使用温度:约40℃。商品尺寸(cm):宽约23.3×深约21.3×高约27.7(主体尺寸) 商品质量:2.4kg(包括软管、手提工具)
-配件:手持工具、真空软管、清洁刷、电池×2、充电适配器 ※1 充满电、电池初期温度:20℃</t>
+          <t>【启动仅需20秒!】 GOBOT的蒸汽拖把，从通电到蒸汽喷射准备就绪仅需约20秒。可以随时使用。通过高温蒸汽的强弱选择，可以有效去除需要清洁的地方的污垢。
+【3种方式轻松清洁】组合丰富的零件，只需一台即可用于多个场所。可以清洁厨房的油污、洗面台的水垢、浴室的霉菌等，能够多样化地清洁宽阔的地面和细小的地方。
+【每分钟30克的超高蒸汽喷射量】以100°C的高温大量喷射蒸汽，轻松去除顽固污垢。蒸汽喷射量可以调节为强或弱，因此可以根据地板类型和污垢情况进行选择。弱模式适用于清洁地板、地毯、床等表面。高温蒸汽不仅可以去除污垢，还可以消除异味，因此小孩和宠物也可以在清洁的地板上安全地度过。
+【丰富的附件让家中闪闪发光】配备了丰富的15个附件。可以用于清扫地板、灶台、抽油烟机、水槽、浴室、玄关、窗户、卫生间、空调等各种场所。从日常清洁到顽固污渍的清洁，只需这一台就能让整个家闪闪发光。
+非常轻便，易于操作！】主体重量仅1.2千克，即使是女性和老年人也能轻松清洁。将电源插头连接到插座后约20秒即可使用。此外，使用拖把时所用的拖把管采用轻便强韧且导热性优良的铝材。
+[约5米长绳,可动范围广]作为拖把使用时的头部有广泛的可动范围,因此您可以在不弯腰的情况下清洁家具下方等各种场所。</t>
         </is>
       </c>
       <c r="J40" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0BL6RYNQ2?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0H89ZR9LV?psc=1</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31i885y+FLL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31sEmiQ15AL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L40" s="12" t="inlineStr">
         <is>
-          <t>B0BL6RYNQ2</t>
+          <t>B0H89ZR9LV</t>
         </is>
       </c>
       <c r="M40" s="12" t="inlineStr">
@@ -17858,13 +17759,13 @@
         </is>
       </c>
       <c r="O40" s="13">
-        <v>49708</v>
+        <v>42971</v>
       </c>
       <c r="P40" s="13">
-        <v>63857</v>
+        <v>22167</v>
       </c>
       <c r="Q40" s="14">
-        <v>0.39</v>
+        <v>0.36</v>
       </c>
       <c r="R40" s="15" t="inlineStr">
         <is>
@@ -17873,17 +17774,15 @@
       </c>
       <c r="S40" s="16" t="inlineStr">
         <is>
-          <t>35</t>
+          <t>32</t>
         </is>
       </c>
       <c r="T40" s="13">
-        <v>28</v>
-      </c>
-      <c r="U40" s="14">
-        <v>-0.18</v>
-      </c>
+        <v>33</v>
+      </c>
+      <c r="U40" s="14"/>
       <c r="V40" s="13">
-        <v>436800</v>
+        <v>391050</v>
       </c>
       <c r="W40" s="13"/>
       <c r="X40" s="13"/>
@@ -17891,37 +17790,37 @@
         <v>1</v>
       </c>
       <c r="Z40" s="13">
-        <v>15600</v>
+        <v>11850</v>
       </c>
       <c r="AA40" s="2"/>
       <c r="AB40" s="1"/>
       <c r="AC40" s="2"/>
       <c r="AD40" s="17">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE40" s="13">
         <v>1</v>
       </c>
       <c r="AF40" s="18">
-        <v>3.5</v>
+        <v>5</v>
       </c>
       <c r="AG40" s="19">
-        <v>0.035699999999999996</v>
+        <v>0.030299999999999997</v>
       </c>
       <c r="AH40" s="13">
-        <v>675</v>
+        <v>1020</v>
       </c>
       <c r="AI40" s="14">
-        <v>0.81</v>
+        <v>0.75</v>
       </c>
       <c r="AJ40"/>
       <c r="AK40" s="11" t="inlineStr">
         <is>
-          <t>2022-11-18</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AL40" s="17">
-        <v>1410</v>
+        <v>28</v>
       </c>
       <c r="AM40" s="11" t="inlineStr">
         <is>
@@ -17931,15 +17830,13 @@
       <c r="AN40" s="11"/>
       <c r="AO40" s="11"/>
       <c r="AP40" s="2"/>
-      <c r="AQ40" s="17">
-        <v>5</v>
-      </c>
+      <c r="AQ40" s="17"/>
       <c r="AR40" s="17">
-        <v>14</v>
+        <v>1</v>
       </c>
       <c r="AS40" s="12" t="inlineStr">
         <is>
-          <t>KUMAMON</t>
+          <t>GOBOT</t>
         </is>
       </c>
       <c r="AT40" s="11" t="inlineStr">
@@ -17954,12 +17851,12 @@
       </c>
       <c r="AV40" s="12" t="inlineStr">
         <is>
-          <t>熊本県熊 8618039 JP</t>
+          <t>横浜市中区 神奈川県 2310861 JP</t>
         </is>
       </c>
       <c r="AW40" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2GDOHXNU39HXM</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KZHF5181BFVZ</t>
         </is>
       </c>
       <c r="AX40" s="11"/>
@@ -17967,7 +17864,11 @@
       <c r="AZ40" s="11"/>
       <c r="BA40" s="11"/>
       <c r="BB40" s="11"/>
-      <c r="BC40" s="11"/>
+      <c r="BC40" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BD40" s="11"/>
       <c r="BE40" s="11"/>
       <c r="BF40" s="11"/>
@@ -17976,42 +17877,34 @@
       <c r="BI40" s="20"/>
       <c r="BJ40" s="20" t="inlineStr">
         <is>
-          <t>3.54 Kilograms</t>
+          <t>16 Kilograms</t>
         </is>
       </c>
       <c r="BK40" s="20" t="inlineStr">
         <is>
-          <t>3.54 kg</t>
-        </is>
-      </c>
-      <c r="BL40" s="20" t="inlineStr">
-        <is>
-          <t>39.4 x 28 x 26.8 cm</t>
-        </is>
-      </c>
-      <c r="BM40" s="20" t="inlineStr">
-        <is>
-          <t>39.40 x 28.00 x 26.80 cm</t>
-        </is>
-      </c>
+          <t>16.00 kg</t>
+        </is>
+      </c>
+      <c r="BL40" s="20"/>
+      <c r="BM40" s="20"/>
       <c r="BN40" s="20" t="inlineStr">
         <is>
-          <t>3.54 kg</t>
+          <t>16 kg</t>
         </is>
       </c>
       <c r="BO40" s="20" t="inlineStr">
         <is>
-          <t>3.54 kg</t>
+          <t>16.00 kg</t>
         </is>
       </c>
       <c r="BP40" s="20" t="inlineStr">
         <is>
-          <t>39.4 x 28 x 26.8 cm</t>
+          <t>57 x 41 x 32 cm</t>
         </is>
       </c>
       <c r="BQ40" s="20" t="inlineStr">
         <is>
-          <t>39.40 x 28.00 x 26.80 cm</t>
+          <t>57.00 x 41.00 x 32.00 cm</t>
         </is>
       </c>
       <c r="BR40" s="11" t="inlineStr">
@@ -18027,256 +17920,35 @@
       <c r="B41" s="11"/>
       <c r="C41" s="12" t="inlineStr">
         <is>
-          <t>B0H89ZR9LV</t>
-        </is>
-      </c>
-      <c r="D41" s="12"/>
+          <t>B0GF8HHWYQ</t>
+        </is>
+      </c>
+      <c r="D41" s="12" t="inlineStr">
+        <is>
+          <t>颜色: 白</t>
+        </is>
+      </c>
       <c r="E41" s="12" t="inlineStr">
         <is>
-          <t>品牌: GOBOT | 型号名称: GBT-G005 | 随附部件: 蒸汽头附件 | 外型规格: 拖把 | 加热时间: 20 秒</t>
+          <t>品牌: M Mistsince | 特殊功能: 重量轻, 锁定开关, 高压力 | 随附部件: squeasy、Shutt吸嘴, 布用喷嘴盖、金属垫圈套, 软管、金属环、金属涂层底座, 量杯、收纳袋, 黄铜刷、尼龙刷、间隙刷 | 瓦数: 1000 瓦特 | 外型规格: 手持式</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
         <is>
-          <t>GOBOT</t>
+          <t>M Mistsince</t>
         </is>
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/GOBOT/b/ref=bl_dp_s_web_7090029051?ie=UTF8&amp;node=7090029051&amp;field-lbr_brands_browse-bin=GOBOT</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/Mistsince/page/D3BF9035-65AB-4860-9B3C-F101376ACA73?lp_asin=B0GF8HHWYQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>GOBOT 蒸汽清洁器 20秒待机 蒸汽拖把 可调节蒸汽量 轻量 地板清洁 高温蒸汽 清洁 水擦拭 蒸汽吸尘器 厨房清洁</t>
+          <t>Mistsince 蒸汽清洁器 手持式 15件套 高压蒸汽清洗 轻量型 家用 便携式 厨房清洁 浴室清洁 榻榻米 油污 水垢 年末清洁 除菌</t>
         </is>
       </c>
       <c r="I41" s="12" t="inlineStr">
-        <is>
-          <t>【启动仅需20秒!】 GOBOT的蒸汽拖把，从通电到蒸汽喷射准备就绪仅需约20秒。可以随时使用。通过高温蒸汽的强弱选择，可以有效去除需要清洁的地方的污垢。
-【3种方式轻松清洁】组合丰富的零件，只需一台即可用于多个场所。可以清洁厨房的油污、洗面台的水垢、浴室的霉菌等，能够多样化地清洁宽阔的地面和细小的地方。
-【每分钟30克的超高蒸汽喷射量】以100°C的高温大量喷射蒸汽，轻松去除顽固污垢。蒸汽喷射量可以调节为强或弱，因此可以根据地板类型和污垢情况进行选择。弱模式适用于清洁地板、地毯、床等表面。高温蒸汽不仅可以去除污垢，还可以消除异味，因此小孩和宠物也可以在清洁的地板上安全地度过。
-【丰富的附件让家中闪闪发光】配备了丰富的15个附件。可以用于清扫地板、灶台、抽油烟机、水槽、浴室、玄关、窗户、卫生间、空调等各种场所。从日常清洁到顽固污渍的清洁，只需这一台就能让整个家闪闪发光。
-非常轻便，易于操作！】主体重量仅1.2千克，即使是女性和老年人也能轻松清洁。将电源插头连接到插座后约20秒即可使用。此外，使用拖把时所用的拖把管采用轻便强韧且导热性优良的铝材。
-[约5米长绳,可动范围广]作为拖把使用时的头部有广泛的可动范围,因此您可以在不弯腰的情况下清洁家具下方等各种场所。</t>
-        </is>
-      </c>
-      <c r="J41" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0H89ZR9LV?psc=1</t>
-        </is>
-      </c>
-      <c r="K41" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31sEmiQ15AL._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L41" s="12" t="inlineStr">
-        <is>
-          <t>B0H89ZR9LV</t>
-        </is>
-      </c>
-      <c r="M41" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:清洁机</t>
-        </is>
-      </c>
-      <c r="N41" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O41" s="13">
-        <v>42971</v>
-      </c>
-      <c r="P41" s="13">
-        <v>22167</v>
-      </c>
-      <c r="Q41" s="14">
-        <v>0.36</v>
-      </c>
-      <c r="R41" s="15" t="inlineStr">
-        <is>
-          <t>电动清洗机\\\\清洁机</t>
-        </is>
-      </c>
-      <c r="S41" s="16" t="inlineStr">
-        <is>
-          <t>32</t>
-        </is>
-      </c>
-      <c r="T41" s="13">
-        <v>33</v>
-      </c>
-      <c r="U41" s="14"/>
-      <c r="V41" s="13">
-        <v>391050</v>
-      </c>
-      <c r="W41" s="13"/>
-      <c r="X41" s="13"/>
-      <c r="Y41" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z41" s="13">
-        <v>11850</v>
-      </c>
-      <c r="AA41" s="2"/>
-      <c r="AB41" s="1"/>
-      <c r="AC41" s="2"/>
-      <c r="AD41" s="17">
-        <v>3</v>
-      </c>
-      <c r="AE41" s="13">
-        <v>1</v>
-      </c>
-      <c r="AF41" s="18">
-        <v>5</v>
-      </c>
-      <c r="AG41" s="19">
-        <v>0.030299999999999997</v>
-      </c>
-      <c r="AH41" s="13">
-        <v>1020</v>
-      </c>
-      <c r="AI41" s="14">
-        <v>0.75</v>
-      </c>
-      <c r="AJ41"/>
-      <c r="AK41" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="AL41" s="17">
-        <v>28</v>
-      </c>
-      <c r="AM41" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN41" s="11"/>
-      <c r="AO41" s="11"/>
-      <c r="AP41" s="2"/>
-      <c r="AQ41" s="17"/>
-      <c r="AR41" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS41" s="12" t="inlineStr">
-        <is>
-          <t>GOBOT</t>
-        </is>
-      </c>
-      <c r="AT41" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU41" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV41" s="12" t="inlineStr">
-        <is>
-          <t>横浜市中区 神奈川県 2310861 JP</t>
-        </is>
-      </c>
-      <c r="AW41" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KZHF5181BFVZ</t>
-        </is>
-      </c>
-      <c r="AX41" s="11"/>
-      <c r="AY41" s="11"/>
-      <c r="AZ41" s="11"/>
-      <c r="BA41" s="11"/>
-      <c r="BB41" s="11"/>
-      <c r="BC41" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD41" s="11"/>
-      <c r="BE41" s="11"/>
-      <c r="BF41" s="11"/>
-      <c r="BG41" s="11"/>
-      <c r="BH41" s="12"/>
-      <c r="BI41" s="20"/>
-      <c r="BJ41" s="20" t="inlineStr">
-        <is>
-          <t>16 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK41" s="20" t="inlineStr">
-        <is>
-          <t>16.00 kg</t>
-        </is>
-      </c>
-      <c r="BL41" s="20"/>
-      <c r="BM41" s="20"/>
-      <c r="BN41" s="20" t="inlineStr">
-        <is>
-          <t>16 kg</t>
-        </is>
-      </c>
-      <c r="BO41" s="20" t="inlineStr">
-        <is>
-          <t>16.00 kg</t>
-        </is>
-      </c>
-      <c r="BP41" s="20" t="inlineStr">
-        <is>
-          <t>57 x 41 x 32 cm</t>
-        </is>
-      </c>
-      <c r="BQ41" s="20" t="inlineStr">
-        <is>
-          <t>57.00 x 41.00 x 32.00 cm</t>
-        </is>
-      </c>
-      <c r="BR41" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="11">
-        <v>41</v>
-      </c>
-      <c r="B42" s="11"/>
-      <c r="C42" s="12" t="inlineStr">
-        <is>
-          <t>B0GF8HHWYQ</t>
-        </is>
-      </c>
-      <c r="D42" s="12" t="inlineStr">
-        <is>
-          <t>颜色: 白</t>
-        </is>
-      </c>
-      <c r="E42" s="12" t="inlineStr">
-        <is>
-          <t>品牌: M Mistsince | 特殊功能: 重量轻, 锁定开关, 高压力 | 随附部件: squeasy、Shutt吸嘴, 布用喷嘴盖、金属垫圈套, 软管、金属环、金属涂层底座, 量杯、收纳袋, 黄铜刷、尼龙刷、间隙刷 | 瓦数: 1000 瓦特 | 外型规格: 手持式</t>
-        </is>
-      </c>
-      <c r="F42" s="12" t="inlineStr">
-        <is>
-          <t>M Mistsince</t>
-        </is>
-      </c>
-      <c r="G42" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/Mistsince/page/D3BF9035-65AB-4860-9B3C-F101376ACA73?lp_asin=B0GF8HHWYQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H42" s="12" t="inlineStr">
-        <is>
-          <t>Mistsince 蒸汽清洁器 手持式 15件套 高压蒸汽清洗 轻量型 家用 便携式 厨房清洁 浴室清洁 榻榻米 油污 水垢 年末清洁 除菌</t>
-        </is>
-      </c>
-      <c r="I42" s="12" t="inlineStr">
         <is>
           <t>♨『正宗锅炉式，3气压稳定高压蒸汽喷射强力清洁』锅炉式加热方式通过内部结构增强蒸汽喷射压力，实现更强的清洁力，从而提高清洁效率。 与速热式面板型蒸汽清洁器相比，能持续喷射稳定的高温蒸汽，非常适合大扫除
 ♨『单靠水进行除菌』只需将水倒入约3分钟后即可开始使用蒸汽。 通过约110°C的高温蒸汽,轻松去除油渍。 彻底去除烧焦和换气扇的顽固污垢。
@@ -18285,19 +17957,262 @@
 【家庭用轻量款】专门用于家庭使用而开发的轻量款,比市售的主流便携式蒸汽清洁机轻约300克。 针对家庭使用场景进行了优化，减轻手部疲劳。 约360厘米的电源线，可轻松清洁整个家。</t>
         </is>
       </c>
+      <c r="J41" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0GF8HHWYQ?psc=1</t>
+        </is>
+      </c>
+      <c r="K41" s="12" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41z5edZXbeL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L41" s="12" t="inlineStr">
+        <is>
+          <t>B0GXYJC1JK</t>
+        </is>
+      </c>
+      <c r="M41" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装:消费性电子产品:电器:清洁机</t>
+        </is>
+      </c>
+      <c r="N41" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装</t>
+        </is>
+      </c>
+      <c r="O41" s="13">
+        <v>34800</v>
+      </c>
+      <c r="P41" s="13">
+        <v>-101016</v>
+      </c>
+      <c r="Q41" s="14">
+        <v>-1.06</v>
+      </c>
+      <c r="R41" s="15" t="inlineStr">
+        <is>
+          <t>电动清洗机\\\\清洁机</t>
+        </is>
+      </c>
+      <c r="S41" s="16" t="inlineStr">
+        <is>
+          <t>26</t>
+        </is>
+      </c>
+      <c r="T41" s="13">
+        <v>46</v>
+      </c>
+      <c r="U41" s="14">
+        <v>0.13</v>
+      </c>
+      <c r="V41" s="13">
+        <v>349186</v>
+      </c>
+      <c r="W41" s="13"/>
+      <c r="X41" s="13"/>
+      <c r="Y41" s="17">
+        <v>3</v>
+      </c>
+      <c r="Z41" s="13">
+        <v>7591</v>
+      </c>
+      <c r="AA41" s="2"/>
+      <c r="AB41" s="1"/>
+      <c r="AC41" s="2"/>
+      <c r="AD41" s="17">
+        <v>23</v>
+      </c>
+      <c r="AE41" s="13">
+        <v>6</v>
+      </c>
+      <c r="AF41" s="18">
+        <v>4.3</v>
+      </c>
+      <c r="AG41" s="19">
+        <v>0.1304</v>
+      </c>
+      <c r="AH41" s="13">
+        <v>472</v>
+      </c>
+      <c r="AI41" s="14">
+        <v>0.79</v>
+      </c>
+      <c r="AJ41"/>
+      <c r="AK41" s="11" t="inlineStr">
+        <is>
+          <t>2026-04-18</t>
+        </is>
+      </c>
+      <c r="AL41" s="17">
+        <v>162</v>
+      </c>
+      <c r="AM41" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN41" s="11"/>
+      <c r="AO41" s="11"/>
+      <c r="AP41" s="2"/>
+      <c r="AQ41" s="17">
+        <v>10</v>
+      </c>
+      <c r="AR41" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS41" s="12" t="inlineStr">
+        <is>
+          <t>Mistsince</t>
+        </is>
+      </c>
+      <c r="AT41" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU41" s="11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV41" s="12" t="inlineStr">
+        <is>
+          <t>Jiangsu 226511 CN</t>
+        </is>
+      </c>
+      <c r="AW41" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AVZ7LMXDP1WK4</t>
+        </is>
+      </c>
+      <c r="AX41" s="11"/>
+      <c r="AY41" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AZ41" s="11"/>
+      <c r="BA41" s="11"/>
+      <c r="BB41" s="11"/>
+      <c r="BC41" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD41" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE41" s="11"/>
+      <c r="BF41" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG41" s="11"/>
+      <c r="BH41" s="12"/>
+      <c r="BI41" s="20" t="inlineStr">
+        <is>
+          <t>Amazon おすすめ</t>
+        </is>
+      </c>
+      <c r="BJ41" s="20" t="inlineStr">
+        <is>
+          <t>2.55 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK41" s="20" t="inlineStr">
+        <is>
+          <t>2.55 kg</t>
+        </is>
+      </c>
+      <c r="BL41" s="20" t="inlineStr">
+        <is>
+          <t>10奥行き x 20幅 x 10高さ cm</t>
+        </is>
+      </c>
+      <c r="BM41" s="20"/>
+      <c r="BN41" s="20" t="inlineStr">
+        <is>
+          <t>2.55 kg</t>
+        </is>
+      </c>
+      <c r="BO41" s="20" t="inlineStr">
+        <is>
+          <t>2.55 kg</t>
+        </is>
+      </c>
+      <c r="BP41" s="20" t="inlineStr">
+        <is>
+          <t>39.8 x 24.9 x 13.6 cm</t>
+        </is>
+      </c>
+      <c r="BQ41" s="20" t="inlineStr">
+        <is>
+          <t>39.80 x 24.90 x 13.60 cm</t>
+        </is>
+      </c>
+      <c r="BR41" s="11" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A42" s="11">
+        <v>41</v>
+      </c>
+      <c r="B42" s="11"/>
+      <c r="C42" s="12" t="inlineStr">
+        <is>
+          <t>B0B3XBM5HW</t>
+        </is>
+      </c>
+      <c r="D42" s="12"/>
+      <c r="E42" s="12" t="inlineStr">
+        <is>
+          <t>品牌: KÄRCHER | 特殊功能: 紧凑型设计 | 推荐表面: 地毯、地板、厨房、浴室、玄关、厕所、车、衣服 | 型号名称: SC MINI | 随附部件: 无</t>
+        </is>
+      </c>
+      <c r="F42" s="12" t="inlineStr">
+        <is>
+          <t>KÄRCHER</t>
+        </is>
+      </c>
+      <c r="G42" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/stores/%E3%82%B1%E3%83%AB%E3%83%92%E3%83%A3%E3%83%BCKARCHER/page/C3335239-5EF7-43A7-B432-CEBBBE4E3C9B?lp_asin=B0B3XBM5HW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+        </is>
+      </c>
+      <c r="H42" s="12" t="inlineStr">
+        <is>
+          <t>凯尔欣（Karcher）蒸汽清洁器 SC MINI 适合日常小型使用的紧凑型号 便携 轻量 高温稳定的蒸汽锅炉加热 浮起顽固污垢 只用水消毒除臭 油污 地毯 干净地板 水垢 厨房 浴室 玄关 厕所 车 衣物 配件齐全 选配配件丰富 1.516-339.0</t>
+        </is>
+      </c>
+      <c r="I42" s="12" t="inlineStr">
+        <is>
+          <t>尺寸:321×127×186毫米。材质:ABS树脂。升温时间:约3分钟。
+蒸汽连续喷射时间:约6分钟 电源线:4米 耗电量:1200W
+电源:100V(50Hz/60Hz通用) 本体重量:1.6kg 标准配件:手持刷、2片微纤维罩
+数量:1台</t>
+        </is>
+      </c>
       <c r="J42" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0GF8HHWYQ?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0B3XBM5HW?psc=1</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41z5edZXbeL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/51Sf-O7BUfL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L42" s="12" t="inlineStr">
         <is>
-          <t>B0GXYJC1JK</t>
+          <t>B0B3XBM5HW</t>
         </is>
       </c>
       <c r="M42" s="12" t="inlineStr">
@@ -18311,13 +18226,13 @@
         </is>
       </c>
       <c r="O42" s="13">
-        <v>34800</v>
+        <v>36940</v>
       </c>
       <c r="P42" s="13">
-        <v>-101016</v>
+        <v>123001</v>
       </c>
       <c r="Q42" s="14">
-        <v>-1.06</v>
+        <v>0.71</v>
       </c>
       <c r="R42" s="15" t="inlineStr">
         <is>
@@ -18326,55 +18241,55 @@
       </c>
       <c r="S42" s="16" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>28</t>
         </is>
       </c>
       <c r="T42" s="13">
-        <v>46</v>
+        <v>39</v>
       </c>
       <c r="U42" s="14">
-        <v>0.13</v>
+        <v>-0.34</v>
       </c>
       <c r="V42" s="13">
-        <v>349186</v>
+        <v>222222</v>
       </c>
       <c r="W42" s="13"/>
       <c r="X42" s="13"/>
       <c r="Y42" s="17">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Z42" s="13">
-        <v>7591</v>
+        <v>5698</v>
       </c>
       <c r="AA42" s="2"/>
       <c r="AB42" s="1"/>
       <c r="AC42" s="2"/>
       <c r="AD42" s="17">
-        <v>23</v>
+        <v>42</v>
       </c>
       <c r="AE42" s="13">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AF42" s="18">
-        <v>4.3</v>
+        <v>3.7</v>
       </c>
       <c r="AG42" s="19">
-        <v>0.1304</v>
+        <v>0</v>
       </c>
       <c r="AH42" s="13">
         <v>472</v>
       </c>
       <c r="AI42" s="14">
-        <v>0.79</v>
+        <v>0.77</v>
       </c>
       <c r="AJ42"/>
       <c r="AK42" s="11" t="inlineStr">
         <is>
-          <t>2026-04-18</t>
+          <t>2022-06-13</t>
         </is>
       </c>
       <c r="AL42" s="17">
-        <v>162</v>
+        <v>1568</v>
       </c>
       <c r="AM42" s="11" t="inlineStr">
         <is>
@@ -18385,14 +18300,14 @@
       <c r="AO42" s="11"/>
       <c r="AP42" s="2"/>
       <c r="AQ42" s="17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AR42" s="17">
-        <v>1</v>
+        <v>32</v>
       </c>
       <c r="AS42" s="12" t="inlineStr">
         <is>
-          <t>Mistsince</t>
+          <t>コレクターズマーケット通販事業部【インボイス対応・適格請求書発行事業者】【安心返金保障】</t>
         </is>
       </c>
       <c r="AT42" s="11" t="inlineStr">
@@ -18402,85 +18317,61 @@
       </c>
       <c r="AU42" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV42" s="12" t="inlineStr">
         <is>
-          <t>Jiangsu 226511 CN</t>
+          <t>松戸市 千葉県 2710061 JP</t>
         </is>
       </c>
       <c r="AW42" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AVZ7LMXDP1WK4</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EFLM9LIB8P2E</t>
         </is>
       </c>
       <c r="AX42" s="11"/>
-      <c r="AY42" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY42" s="11"/>
       <c r="AZ42" s="11"/>
       <c r="BA42" s="11"/>
       <c r="BB42" s="11"/>
-      <c r="BC42" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD42" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC42" s="11"/>
+      <c r="BD42" s="11"/>
       <c r="BE42" s="11"/>
-      <c r="BF42" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF42" s="11"/>
       <c r="BG42" s="11"/>
       <c r="BH42" s="12"/>
-      <c r="BI42" s="20" t="inlineStr">
-        <is>
-          <t>Amazon おすすめ</t>
-        </is>
-      </c>
+      <c r="BI42" s="20"/>
       <c r="BJ42" s="20" t="inlineStr">
         <is>
-          <t>2.55 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK42" s="20" t="inlineStr">
-        <is>
-          <t>2.55 kg</t>
-        </is>
-      </c>
+          <t>1.6 千克</t>
+        </is>
+      </c>
+      <c r="BK42" s="20"/>
       <c r="BL42" s="20" t="inlineStr">
         <is>
-          <t>10奥行き x 20幅 x 10高さ cm</t>
+          <t>35 x 321 x 127 x 186 mm</t>
         </is>
       </c>
       <c r="BM42" s="20"/>
       <c r="BN42" s="20" t="inlineStr">
         <is>
-          <t>2.55 kg</t>
+          <t>2.11 kg</t>
         </is>
       </c>
       <c r="BO42" s="20" t="inlineStr">
         <is>
-          <t>2.55 kg</t>
+          <t>2.11 kg</t>
         </is>
       </c>
       <c r="BP42" s="20" t="inlineStr">
         <is>
-          <t>39.8 x 24.9 x 13.6 cm</t>
+          <t>35.9 x 19.3 x 14.5 cm</t>
         </is>
       </c>
       <c r="BQ42" s="20" t="inlineStr">
         <is>
-          <t>39.80 x 24.90 x 13.60 cm</t>
+          <t>35.90 x 19.30 x 14.50 cm</t>
         </is>
       </c>
       <c r="BR42" s="11" t="inlineStr">
@@ -18496,51 +18387,48 @@
       <c r="B43" s="11"/>
       <c r="C43" s="12" t="inlineStr">
         <is>
-          <t>B0B3XBM5HW</t>
+          <t>B0HBNN64GG</t>
         </is>
       </c>
       <c r="D43" s="12"/>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>品牌: KÄRCHER | 特殊功能: 紧凑型设计 | 推荐表面: 地毯、地板、厨房、浴室、玄关、厕所、车、衣服 | 型号名称: SC MINI | 随附部件: 无</t>
+          <t>品牌: PROSTREET | 特殊功能: 4種類のクリーナーモード搭載 | 推荐表面: カーペット | 随附部件: 用户手册, 蒸汽头附件 | 外型规格: 箱式</t>
         </is>
       </c>
       <c r="F43" s="12" t="inlineStr">
         <is>
-          <t>KÄRCHER</t>
+          <t>PROSTREET</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/stores/%E3%82%B1%E3%83%AB%E3%83%92%E3%83%A3%E3%83%BCKARCHER/page/C3335239-5EF7-43A7-B432-CEBBBE4E3C9B?lp_asin=B0B3XBM5HW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=PROSTREET</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>凯尔欣（Karcher）蒸汽清洁器 SC MINI 适合日常小型使用的紧凑型号 便携 轻量 高温稳定的蒸汽锅炉加热 浮起顽固污垢 只用水消毒除臭 油污 地毯 干净地板 水垢 厨房 浴室 玄关 厕所 车 衣物 配件齐全 选配配件丰富 1.516-339.0</t>
+          <t>[SNS上热门话题] New PROSTREET Steam Rinser Cleaner Pro Street 60摄氏度 温水 100摄氏度 蒸汽 清洁器 吸尘器 j汽车清洁剂 地毯清洁器 窗帘 沙发 厨房 床垫 车 高温清洗 强力吸力 大容量水箱 日语指南</t>
         </is>
       </c>
       <c r="I43" s="12" t="inlineStr">
         <is>
-          <t>尺寸:321×127×186毫米。材质:ABS树脂。升温时间:约3分钟。
-蒸汽连续喷射时间:约6分钟 电源线:4米 耗电量:1200W
-电源:100V(50Hz/60Hz通用) 本体重量:1.6kg 标准配件:手持刷、2片微纤维罩
-数量:1台</t>
+          <t>推荐用于清洁地毯、汽车座椅、沙发、窗帘、厨房、洗手间、窗户等。 高温60℃热水,与常温水相比,纤维皮脂污垢会大大不同。 不使用洗涤剂可以温和地清洗儿童过敏。 ◆特征 ①高温60℃温水清洗 ②100℃蒸汽清洗 ③强力地毯清洁器 350W 10kpa ④大容量水箱 ⑤4种清洁模式 ⑤令人放心的日语指南 ⑥ 放心的制造商销售 ⑦ 制造商保修</t>
         </is>
       </c>
       <c r="J43" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0B3XBM5HW?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HBNN64GG?psc=1</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/51Sf-O7BUfL._AC_US600_.jpg</t>
+          <t>https://images-na.ssl-images-amazon.com/images/I/61SWPhDh01L._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L43" s="12" t="inlineStr">
         <is>
-          <t>B0B3XBM5HW</t>
+          <t>B0HBNN64GG</t>
         </is>
       </c>
       <c r="M43" s="12" t="inlineStr">
@@ -18554,13 +18442,13 @@
         </is>
       </c>
       <c r="O43" s="13">
-        <v>36940</v>
+        <v>60774</v>
       </c>
       <c r="P43" s="13">
-        <v>123001</v>
+        <v>-18914</v>
       </c>
       <c r="Q43" s="14">
-        <v>0.71</v>
+        <v>-0.17</v>
       </c>
       <c r="R43" s="15" t="inlineStr">
         <is>
@@ -18569,17 +18457,15 @@
       </c>
       <c r="S43" s="16" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>43</t>
         </is>
       </c>
       <c r="T43" s="13">
-        <v>39</v>
-      </c>
-      <c r="U43" s="14">
-        <v>-0.34</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="U43" s="14"/>
       <c r="V43" s="13">
-        <v>222222</v>
+        <v>140000</v>
       </c>
       <c r="W43" s="13"/>
       <c r="X43" s="13"/>
@@ -18587,37 +18473,37 @@
         <v>1</v>
       </c>
       <c r="Z43" s="13">
-        <v>5698</v>
+        <v>14000</v>
       </c>
       <c r="AA43" s="2"/>
       <c r="AB43" s="1"/>
       <c r="AC43" s="2"/>
       <c r="AD43" s="17">
-        <v>42</v>
+        <v>22</v>
       </c>
       <c r="AE43" s="13">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AF43" s="18">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="AG43" s="19">
         <v>0</v>
       </c>
       <c r="AH43" s="13">
-        <v>472</v>
+        <v>781</v>
       </c>
       <c r="AI43" s="14">
-        <v>0.77</v>
+        <v>0.79</v>
       </c>
       <c r="AJ43"/>
       <c r="AK43" s="11" t="inlineStr">
         <is>
-          <t>2022-06-13</t>
+          <t>2026-08-17</t>
         </is>
       </c>
       <c r="AL43" s="17">
-        <v>1568</v>
+        <v>42</v>
       </c>
       <c r="AM43" s="11" t="inlineStr">
         <is>
@@ -18631,11 +18517,11 @@
         <v>7</v>
       </c>
       <c r="AR43" s="17">
-        <v>32</v>
+        <v>1</v>
       </c>
       <c r="AS43" s="12" t="inlineStr">
         <is>
-          <t>コレクターズマーケット通販事業部【インボイス対応・適格請求書発行事業者】【安心返金保障】</t>
+          <t>株式会社PROSTREET</t>
         </is>
       </c>
       <c r="AT43" s="11" t="inlineStr">
@@ -18650,16 +18536,20 @@
       </c>
       <c r="AV43" s="12" t="inlineStr">
         <is>
-          <t>松戸市 千葉県 2710061 JP</t>
+          <t>大阪府 5918007 JP</t>
         </is>
       </c>
       <c r="AW43" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EFLM9LIB8P2E</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YO7910ANGPIW</t>
         </is>
       </c>
       <c r="AX43" s="11"/>
-      <c r="AY43" s="11"/>
+      <c r="AY43" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="AZ43" s="11"/>
       <c r="BA43" s="11"/>
       <c r="BB43" s="11"/>
@@ -18669,42 +18559,54 @@
       <c r="BF43" s="11"/>
       <c r="BG43" s="11"/>
       <c r="BH43" s="12"/>
-      <c r="BI43" s="20"/>
+      <c r="BI43" s="20" t="inlineStr">
+        <is>
+          <t>亚马逊 精选</t>
+        </is>
+      </c>
       <c r="BJ43" s="20" t="inlineStr">
         <is>
-          <t>1.6 千克</t>
-        </is>
-      </c>
-      <c r="BK43" s="20"/>
+          <t>4.7 kg</t>
+        </is>
+      </c>
+      <c r="BK43" s="20" t="inlineStr">
+        <is>
+          <t>4.70 kg</t>
+        </is>
+      </c>
       <c r="BL43" s="20" t="inlineStr">
         <is>
-          <t>35 x 321 x 127 x 186 mm</t>
-        </is>
-      </c>
-      <c r="BM43" s="20"/>
+          <t>26 x 32 x 40 cm</t>
+        </is>
+      </c>
+      <c r="BM43" s="20" t="inlineStr">
+        <is>
+          <t>26.00 x 32.00 x 40.00 cm</t>
+        </is>
+      </c>
       <c r="BN43" s="20" t="inlineStr">
         <is>
-          <t>2.11 kg</t>
+          <t>6.2 kg</t>
         </is>
       </c>
       <c r="BO43" s="20" t="inlineStr">
         <is>
-          <t>2.11 kg</t>
+          <t>6.20 kg</t>
         </is>
       </c>
       <c r="BP43" s="20" t="inlineStr">
         <is>
-          <t>35.9 x 19.3 x 14.5 cm</t>
+          <t>41 x 37.5 x 30.8 cm</t>
         </is>
       </c>
       <c r="BQ43" s="20" t="inlineStr">
         <is>
-          <t>35.90 x 19.30 x 14.50 cm</t>
+          <t>41.00 x 37.50 x 30.80 cm</t>
         </is>
       </c>
       <c r="BR43" s="11" t="inlineStr">
         <is>
-          <t>标准</t>
+          <t>大件</t>
         </is>
       </c>
     </row>
@@ -18715,515 +18617,35 @@
       <c r="B44" s="11"/>
       <c r="C44" s="12" t="inlineStr">
         <is>
-          <t>B0HBNN64GG</t>
-        </is>
-      </c>
-      <c r="D44" s="12"/>
+          <t>B0DRCGRJSR</t>
+        </is>
+      </c>
+      <c r="D44" s="12" t="inlineStr">
+        <is>
+          <t>尺寸: Large</t>
+        </is>
+      </c>
       <c r="E44" s="12" t="inlineStr">
         <is>
-          <t>品牌: PROSTREET | 特殊功能: 4種類のクリーナーモード搭載 | 推荐表面: カーペット | 随附部件: 用户手册, 蒸汽头附件 | 外型规格: 箱式</t>
+          <t>品牌: HAUSHOF | 特殊功能: 快速升温 | 随附部件: 刷, 喷嘴, 尼龙刷, 拖把垫, 漏斗 | 瓦数: 1200 瓦特 | 油箱容积: 450 毫升</t>
         </is>
       </c>
       <c r="F44" s="12" t="inlineStr">
         <is>
-          <t>PROSTREET</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=PROSTREET</t>
+          <t>https://www.amazon.co.jp/-/zh/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0DRCGRJSR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>[SNS上热门话题] New PROSTREET Steam Rinser Cleaner Pro Street 60摄氏度 温水 100摄氏度 蒸汽 清洁器 吸尘器 j汽车清洁剂 地毯清洁器 窗帘 沙发 厨房 床垫 车 高温清洗 强力吸力 大容量水箱 日语指南</t>
+          <t>HAUSHOF 【2025新型】 蒸汽清洁器 小型 蒸汽吸尘器 高温蒸汽清汁器 锅炉式加热 配备8件附件的 手持 蒸汽清洗机 100% 天然清洁 完全不使用化学药品 家庭/厨房/汽车/蒸汽清洁/地毯 消毒 清洁 年末大扫除 附专用工具袋</t>
         </is>
       </c>
       <c r="I44" s="12" t="inlineStr">
-        <is>
-          <t>推荐用于清洁地毯、汽车座椅、沙发、窗帘、厨房、洗手间、窗户等。 高温60℃热水,与常温水相比,纤维皮脂污垢会大大不同。 不使用洗涤剂可以温和地清洗儿童过敏。 ◆特征 ①高温60℃温水清洗 ②100℃蒸汽清洗 ③强力地毯清洁器 350W 10kpa ④大容量水箱 ⑤4种清洁模式 ⑤令人放心的日语指南 ⑥ 放心的制造商销售 ⑦ 制造商保修</t>
-        </is>
-      </c>
-      <c r="J44" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HBNN64GG?psc=1</t>
-        </is>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/61SWPhDh01L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>B0HBNN64GG</t>
-        </is>
-      </c>
-      <c r="M44" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:清洁机</t>
-        </is>
-      </c>
-      <c r="N44" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O44" s="13">
-        <v>60774</v>
-      </c>
-      <c r="P44" s="13">
-        <v>-18914</v>
-      </c>
-      <c r="Q44" s="14">
-        <v>-0.17</v>
-      </c>
-      <c r="R44" s="15" t="inlineStr">
-        <is>
-          <t>电动清洗机\\\\清洁机</t>
-        </is>
-      </c>
-      <c r="S44" s="16" t="inlineStr">
-        <is>
-          <t>43</t>
-        </is>
-      </c>
-      <c r="T44" s="13">
-        <v>10</v>
-      </c>
-      <c r="U44" s="14"/>
-      <c r="V44" s="13">
-        <v>140000</v>
-      </c>
-      <c r="W44" s="13"/>
-      <c r="X44" s="13"/>
-      <c r="Y44" s="17">
-        <v>1</v>
-      </c>
-      <c r="Z44" s="13">
-        <v>14000</v>
-      </c>
-      <c r="AA44" s="2"/>
-      <c r="AB44" s="1"/>
-      <c r="AC44" s="2"/>
-      <c r="AD44" s="17">
-        <v>22</v>
-      </c>
-      <c r="AE44" s="13">
-        <v>16</v>
-      </c>
-      <c r="AF44" s="18">
-        <v>4.4</v>
-      </c>
-      <c r="AG44" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH44" s="13">
-        <v>781</v>
-      </c>
-      <c r="AI44" s="14">
-        <v>0.79</v>
-      </c>
-      <c r="AJ44"/>
-      <c r="AK44" s="11" t="inlineStr">
-        <is>
-          <t>2026-08-17</t>
-        </is>
-      </c>
-      <c r="AL44" s="17">
-        <v>42</v>
-      </c>
-      <c r="AM44" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN44" s="11"/>
-      <c r="AO44" s="11"/>
-      <c r="AP44" s="2"/>
-      <c r="AQ44" s="17">
-        <v>7</v>
-      </c>
-      <c r="AR44" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS44" s="12" t="inlineStr">
-        <is>
-          <t>株式会社PROSTREET</t>
-        </is>
-      </c>
-      <c r="AT44" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU44" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV44" s="12" t="inlineStr">
-        <is>
-          <t>大阪府 5918007 JP</t>
-        </is>
-      </c>
-      <c r="AW44" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YO7910ANGPIW</t>
-        </is>
-      </c>
-      <c r="AX44" s="11"/>
-      <c r="AY44" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ44" s="11"/>
-      <c r="BA44" s="11"/>
-      <c r="BB44" s="11"/>
-      <c r="BC44" s="11"/>
-      <c r="BD44" s="11"/>
-      <c r="BE44" s="11"/>
-      <c r="BF44" s="11"/>
-      <c r="BG44" s="11"/>
-      <c r="BH44" s="12"/>
-      <c r="BI44" s="20" t="inlineStr">
-        <is>
-          <t>亚马逊 精选</t>
-        </is>
-      </c>
-      <c r="BJ44" s="20" t="inlineStr">
-        <is>
-          <t>4.7 kg</t>
-        </is>
-      </c>
-      <c r="BK44" s="20" t="inlineStr">
-        <is>
-          <t>4.70 kg</t>
-        </is>
-      </c>
-      <c r="BL44" s="20" t="inlineStr">
-        <is>
-          <t>26 x 32 x 40 cm</t>
-        </is>
-      </c>
-      <c r="BM44" s="20" t="inlineStr">
-        <is>
-          <t>26.00 x 32.00 x 40.00 cm</t>
-        </is>
-      </c>
-      <c r="BN44" s="20" t="inlineStr">
-        <is>
-          <t>6.2 kg</t>
-        </is>
-      </c>
-      <c r="BO44" s="20" t="inlineStr">
-        <is>
-          <t>6.20 kg</t>
-        </is>
-      </c>
-      <c r="BP44" s="20" t="inlineStr">
-        <is>
-          <t>41 x 37.5 x 30.8 cm</t>
-        </is>
-      </c>
-      <c r="BQ44" s="20" t="inlineStr">
-        <is>
-          <t>41.00 x 37.50 x 30.80 cm</t>
-        </is>
-      </c>
-      <c r="BR44" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="11">
-        <v>44</v>
-      </c>
-      <c r="B45" s="11"/>
-      <c r="C45" s="12" t="inlineStr">
-        <is>
-          <t>B08R3LF57P</t>
-        </is>
-      </c>
-      <c r="D45" s="12" t="inlineStr">
-        <is>
-          <t>颜色: B:8片装</t>
-        </is>
-      </c>
-      <c r="E45" s="12" t="inlineStr">
-        <is>
-          <t>品牌: KEEPOW | 特殊功能: 高品质,耐用 | 推荐表面: 水槽, 浴缸, 淋浴房 | 随附部件: 超细纤维盖 | 外型规格: 手持式</t>
-        </is>
-      </c>
-      <c r="F45" s="12" t="inlineStr">
-        <is>
-          <t>KEEPOW</t>
-        </is>
-      </c>
-      <c r="G45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/KEEPOW/page/21523984-F72B-4ED5-8C28-45B0588E2513?lp_asin=B08R3LF57P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
-        </is>
-      </c>
-      <c r="H45" s="12" t="inlineStr">
-        <is>
-          <t>KEEPOW Karcher8片装 消耗品 蒸汽清洁器 手刷用</t>
-        </is>
-      </c>
-      <c r="I45" s="12" t="inlineStr">
-        <is>
-          <t>【对应机型】科尔希尔用 SC MINI、SC 1 MINI、SC 1 EasyFix、SC 1 EasyFix Premium 、SC 1 经典、SC 2 EasyFix、SC 2 EasyFix Premium 、SC 3 EasyFix、SC 3 EasyFix Premium 、SC 4 EasyFix、SG 4/4、SC 4 EasyFi EasyFi EasyFi EasyFix EasyFix EasyFix。 yx 高级 SC 5 EasyFix、SC JTK 10、SC JTK 20
-【高品质】Kelchanus团队清洁剂替换用布部件采用超细纤维制成,污垢的研磨能力和吸尘力、吸水力强,可以彻底清除粘腻污垢。 可手洗、机洗,可重复使用。 请勿使用软剂。
-【速干性和耐用性】Karcher用罩采用小环结构,使用后迅速干燥,抑制细菌和霉菌的产生。 此外,反复使用和洗涤也很强,可长期保持良好的状态。
-【适用场所】洗脸台/水槽、浴室/浴缸、厨房作业台、燃气灶、厨房、换气门、冰箱(内外)、餐具架内侧/抽屉、不锈钢部分
-【包装】超细纤维枕套×8片。</t>
-        </is>
-      </c>
-      <c r="J45" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B08R3LF57P?psc=1</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
-        <is>
-          <t>https://images-na.ssl-images-amazon.com/images/I/41AHQ4cHR8L._AC_US600_.jpg</t>
-        </is>
-      </c>
-      <c r="L45" s="12" t="inlineStr">
-        <is>
-          <t>B0DBHX5TKK</t>
-        </is>
-      </c>
-      <c r="M45" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:清洁机</t>
-        </is>
-      </c>
-      <c r="N45" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O45" s="13">
-        <v>55179</v>
-      </c>
-      <c r="P45" s="13">
-        <v>-3609</v>
-      </c>
-      <c r="Q45" s="14">
-        <v>-0.05</v>
-      </c>
-      <c r="R45" s="15" t="inlineStr">
-        <is>
-          <t>电动清洗机\\\\清洁机</t>
-        </is>
-      </c>
-      <c r="S45" s="16" t="inlineStr">
-        <is>
-          <t>38</t>
-        </is>
-      </c>
-      <c r="T45" s="13">
-        <v>42</v>
-      </c>
-      <c r="U45" s="14"/>
-      <c r="V45" s="13">
-        <v>96558</v>
-      </c>
-      <c r="W45" s="13"/>
-      <c r="X45" s="13"/>
-      <c r="Y45" s="17">
-        <v>4</v>
-      </c>
-      <c r="Z45" s="13">
-        <v>2299</v>
-      </c>
-      <c r="AA45" s="2"/>
-      <c r="AB45" s="1"/>
-      <c r="AC45" s="2"/>
-      <c r="AD45" s="17">
-        <v>262</v>
-      </c>
-      <c r="AE45" s="13">
-        <v>2</v>
-      </c>
-      <c r="AF45" s="18">
-        <v>4</v>
-      </c>
-      <c r="AG45" s="19">
-        <v>0.047599999999999996</v>
-      </c>
-      <c r="AH45" s="13">
-        <v>318</v>
-      </c>
-      <c r="AI45" s="14">
-        <v>0.71</v>
-      </c>
-      <c r="AJ45"/>
-      <c r="AK45" s="11" t="inlineStr">
-        <is>
-          <t>2021-03-04</t>
-        </is>
-      </c>
-      <c r="AL45" s="17">
-        <v>2034</v>
-      </c>
-      <c r="AM45" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN45" s="11"/>
-      <c r="AO45" s="11"/>
-      <c r="AP45" s="2"/>
-      <c r="AQ45" s="17">
-        <v>8</v>
-      </c>
-      <c r="AR45" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS45" s="12" t="inlineStr">
-        <is>
-          <t>Roberts Robot</t>
-        </is>
-      </c>
-      <c r="AT45" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU45" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV45" s="12" t="inlineStr">
-        <is>
-          <t>Guangzhou Guangdong 511442 CN</t>
-        </is>
-      </c>
-      <c r="AW45" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A30T80D6SCTMYZ</t>
-        </is>
-      </c>
-      <c r="AX45" s="11"/>
-      <c r="AY45" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="AZ45" s="11"/>
-      <c r="BA45" s="11"/>
-      <c r="BB45" s="11"/>
-      <c r="BC45" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BD45" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE45" s="11"/>
-      <c r="BF45" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG45" s="11"/>
-      <c r="BH45" s="12"/>
-      <c r="BI45" s="20" t="inlineStr">
-        <is>
-          <t>亚马逊 精选</t>
-        </is>
-      </c>
-      <c r="BJ45" s="20" t="inlineStr">
-        <is>
-          <t>190 g</t>
-        </is>
-      </c>
-      <c r="BK45" s="20" t="inlineStr">
-        <is>
-          <t>190.00 g</t>
-        </is>
-      </c>
-      <c r="BL45" s="20" t="inlineStr">
-        <is>
-          <t>22.5 x 20.3 x 2.8 cm</t>
-        </is>
-      </c>
-      <c r="BM45" s="20" t="inlineStr">
-        <is>
-          <t>22.50 x 20.30 x 2.80 cm</t>
-        </is>
-      </c>
-      <c r="BN45" s="20" t="inlineStr">
-        <is>
-          <t>190 g</t>
-        </is>
-      </c>
-      <c r="BO45" s="20" t="inlineStr">
-        <is>
-          <t>190.00 g</t>
-        </is>
-      </c>
-      <c r="BP45" s="20" t="inlineStr">
-        <is>
-          <t>22.5 x 20.3 x 2.8 cm</t>
-        </is>
-      </c>
-      <c r="BQ45" s="20" t="inlineStr">
-        <is>
-          <t>22.50 x 20.30 x 2.80 cm</t>
-        </is>
-      </c>
-      <c r="BR45" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="11">
-        <v>45</v>
-      </c>
-      <c r="B46" s="11"/>
-      <c r="C46" s="12" t="inlineStr">
-        <is>
-          <t>B0DRCGRJSR</t>
-        </is>
-      </c>
-      <c r="D46" s="12" t="inlineStr">
-        <is>
-          <t>尺寸: Large</t>
-        </is>
-      </c>
-      <c r="E46" s="12" t="inlineStr">
-        <is>
-          <t>品牌: HAUSHOF | 特殊功能: 快速升温 | 随附部件: 刷, 喷嘴, 尼龙刷, 拖把垫, 漏斗 | 瓦数: 1200 瓦特 | 油箱容积: 450 毫升</t>
-        </is>
-      </c>
-      <c r="F46" s="12" t="inlineStr">
-        <is>
-          <t>HAUSHOF</t>
-        </is>
-      </c>
-      <c r="G46" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0DRCGRJSR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override</t>
-        </is>
-      </c>
-      <c r="H46" s="12" t="inlineStr">
-        <is>
-          <t>HAUSHOF 【2025新型】 蒸汽清洁器 小型 蒸汽吸尘器 高温蒸汽清汁器 锅炉式加热 配备8件附件的 手持 蒸汽清洗机 100% 天然清洁 完全不使用化学药品 家庭/厨房/汽车/蒸汽清洁/地毯 消毒 清洁 年末大扫除 附专用工具袋</t>
-        </is>
-      </c>
-      <c r="I46" s="12" t="inlineStr">
         <is>
           <t>【大容量&amp;快速加热】配备450毫升大容量水箱，可连续使用约10~12分钟。 此外，由于采用了锅炉加热系统，加热仅需3~5分钟即可完成，可以立即开始使用。
 【105℃高温加热强力除菌】通过高温蒸汽（105℃）的强力加热模式，有效去除肉眼看不见的细菌和病毒。 创造清洁安全的空间，保护家庭健康。 可以彻底消毒厨房、浴室、地板等各种地方。
@@ -19233,19 +18655,499 @@
 【包装内容】附带丰富的配件，可满足各种清洁需求。 壶*1,量杯*1,布套*1,窗口用塑料*1,喷嘴*1,延长喷嘴*1,烟熏*1,不锈钢塑料容器*1,使用说明书(不一定支持中文)。</t>
         </is>
       </c>
+      <c r="J44" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0DRCGRJSR?psc=1</t>
+        </is>
+      </c>
+      <c r="K44" s="12" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41wLqF+bzbL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L44" s="12" t="inlineStr">
+        <is>
+          <t>B0F486YKK4</t>
+        </is>
+      </c>
+      <c r="M44" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装:消费性电子产品:电器:清洁机</t>
+        </is>
+      </c>
+      <c r="N44" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装</t>
+        </is>
+      </c>
+      <c r="O44" s="13">
+        <v>30451</v>
+      </c>
+      <c r="P44" s="13">
+        <v>65796</v>
+      </c>
+      <c r="Q44" s="14">
+        <v>0.69</v>
+      </c>
+      <c r="R44" s="15" t="inlineStr">
+        <is>
+          <t>电动清洗机\\\\清洁机</t>
+        </is>
+      </c>
+      <c r="S44" s="16" t="inlineStr">
+        <is>
+          <t>24</t>
+        </is>
+      </c>
+      <c r="T44" s="13">
+        <v>16</v>
+      </c>
+      <c r="U44" s="14">
+        <v>-0.97</v>
+      </c>
+      <c r="V44" s="13">
+        <v>95680</v>
+      </c>
+      <c r="W44" s="13"/>
+      <c r="X44" s="13"/>
+      <c r="Y44" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z44" s="13">
+        <v>5980</v>
+      </c>
+      <c r="AA44" s="2"/>
+      <c r="AB44" s="1"/>
+      <c r="AC44" s="2"/>
+      <c r="AD44" s="17">
+        <v>215</v>
+      </c>
+      <c r="AE44" s="13">
+        <v>4</v>
+      </c>
+      <c r="AF44" s="18">
+        <v>4.1</v>
+      </c>
+      <c r="AG44" s="19">
+        <v>0.25</v>
+      </c>
+      <c r="AH44" s="13">
+        <v>472</v>
+      </c>
+      <c r="AI44" s="14">
+        <v>0.77</v>
+      </c>
+      <c r="AJ44"/>
+      <c r="AK44" s="11" t="inlineStr">
+        <is>
+          <t>2025-03-26</t>
+        </is>
+      </c>
+      <c r="AL44" s="17">
+        <v>551</v>
+      </c>
+      <c r="AM44" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN44" s="11"/>
+      <c r="AO44" s="11"/>
+      <c r="AP44" s="2"/>
+      <c r="AQ44" s="17">
+        <v>10</v>
+      </c>
+      <c r="AR44" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS44" s="12" t="inlineStr">
+        <is>
+          <t>Megastar Store</t>
+        </is>
+      </c>
+      <c r="AT44" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU44" s="11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV44" s="12" t="inlineStr">
+        <is>
+          <t>Zhejiang 310019 CN</t>
+        </is>
+      </c>
+      <c r="AW44" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES</t>
+        </is>
+      </c>
+      <c r="AX44" s="11"/>
+      <c r="AY44" s="11"/>
+      <c r="AZ44" s="11"/>
+      <c r="BA44" s="11"/>
+      <c r="BB44" s="11"/>
+      <c r="BC44" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD44" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE44" s="11"/>
+      <c r="BF44" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG44" s="11"/>
+      <c r="BH44" s="12"/>
+      <c r="BI44" s="20"/>
+      <c r="BJ44" s="20" t="inlineStr">
+        <is>
+          <t>2.28 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK44" s="20" t="inlineStr">
+        <is>
+          <t>2.28 kg</t>
+        </is>
+      </c>
+      <c r="BL44" s="20" t="inlineStr">
+        <is>
+          <t>32.3 x 23.9 x 16.3 cm</t>
+        </is>
+      </c>
+      <c r="BM44" s="20" t="inlineStr">
+        <is>
+          <t>32.30 x 23.90 x 16.30 cm</t>
+        </is>
+      </c>
+      <c r="BN44" s="20" t="inlineStr">
+        <is>
+          <t>2.28 kg</t>
+        </is>
+      </c>
+      <c r="BO44" s="20" t="inlineStr">
+        <is>
+          <t>2.28 kg</t>
+        </is>
+      </c>
+      <c r="BP44" s="20" t="inlineStr">
+        <is>
+          <t>32.3 x 23.9 x 16.3 cm</t>
+        </is>
+      </c>
+      <c r="BQ44" s="20" t="inlineStr">
+        <is>
+          <t>32.30 x 23.90 x 16.30 cm</t>
+        </is>
+      </c>
+      <c r="BR44" s="11" t="inlineStr">
+        <is>
+          <t>标准</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A45" s="11">
+        <v>44</v>
+      </c>
+      <c r="B45" s="11"/>
+      <c r="C45" s="12" t="inlineStr">
+        <is>
+          <t>B0HK3489BN</t>
+        </is>
+      </c>
+      <c r="D45" s="12" t="inlineStr">
+        <is>
+          <t>颜色: yellow</t>
+        </is>
+      </c>
+      <c r="E45" s="12" t="inlineStr">
+        <is>
+          <t>品牌: Waitbird | 特殊功能: 120℃の高温蒸気で 99.99% の細菌・ウイルスを除去、4.5Bar 高圧、1500W、ステンレス製ボイラー、角度調整可能なハンドル、21 点多機能アクセサリーセット、急速加熱、蒸気量調整機能、大容量水タンク、動作インジケーターランプ、洗剤不要クリーニング、チャイルドセーフティロック、高効率、時間短縮 | 推荐表面: サニタリー器具、床、タイル目地、ガラス面、シンク、シャワードア、トイレ、布張り家具、キッチンカウンター、コンロ、ソファ、カーテン、車内、カーシート、コーティング済み木製床、ラミネート床、ペット周り、カーペット、壁、窓、タイル、鏡、オーブン、BBQ グリル、シャワー室、浴槽、布地スチーム、ペットベッド、車内細部クリーニング | 随附部件: ナイロンブラシ4本、真鍮ブラシ2本、アイロンタオル3枚、マイクロファイバーモップパッド2枚、延長チューブ2本、計量カップ1個、手袋1個、アイロンブラシ1個、ストラップ1本、ガラスブラシ1個、大型ノズル1個、フロアブラシ1個、カーペットグライダー1個 | 油箱容积: 1100 毫升</t>
+        </is>
+      </c>
+      <c r="F45" s="12" t="inlineStr">
+        <is>
+          <t>Waitbird</t>
+        </is>
+      </c>
+      <c r="G45" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/-/zh/stores/Waitbird/page/3EF06D38-11FF-4AB3-B913-B77B78E9E2C6?lp_asin=B0HK3489BN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+        </is>
+      </c>
+      <c r="H45" s="12" t="inlineStr">
+        <is>
+          <t>Waitbird ハンドスチームクリーナー 120℃高温蒸気除菌 4.5bar 高圧 21 点パーツ</t>
+        </is>
+      </c>
+      <c r="I45" s="12" t="inlineStr">
+        <is>
+          <t>各任務のために21個の部品を完成する：ナイロン工具4個、黄銅工具2個、アイロン布3個、超微細繊維モップマット2個、延長管2本、計量カップ1個、手袋1個、アイロンブラシ1本、ベルト1本、ガラスブラシ1本、大ノズル1個、床ブラシ1本、カーペットキャリッジ1個、あらゆる表面に適用する。（注：スクロールボックスは個別に購入して、特定の要件を満たす必要があります。）
+安全第一、チャイルドロック付きと自動停止：統合チャイルドロックがあり、圧力が安全レベルを超えたり、水位が低くなったりすると、予期せぬ起動と自動停止を防ぐことができる。人間工学に適したハンドルは、長時間使用しても快適な操作を確保することができます。
+全面的な洗浄性能：Waitbirdは248°Fまでの高温蒸気を発生することができ、そして21個の多機能、交換可能な付属品を持ち、専門的に各種表面汚染物を洗浄し、徹底的な360°洗浄を実現し、盲点がない。これにより、ほとんどのアプリケーションシーンがカバーされます。
+38オンスの大水槽とインスタントスチームを使用して時間を節約：待ち時間が短く、清掃時間が長くなる：水は5分以内に248°Fに加熱し、持続的な高圧蒸気供給を提供して、あなたの水位に適応する（最大30オンス/900 mlを提案）。部屋全体を効率的に清潔にし、再充填の手間を最小限に。
+家、車の中、その他の場所での多用途：密封材の清掃、強化フローリング、家電製品、喫煙機、窓、自動車内装、ペットベッド、アウトドアグリル――家庭、車の所有者、ペットの所有者に非常に適している。化学物質のない生活様式の環境保護ソリューション</t>
+        </is>
+      </c>
+      <c r="J45" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/dp/B0HK3489BN?psc=1</t>
+        </is>
+      </c>
+      <c r="K45" s="12" t="inlineStr">
+        <is>
+          <t>https://m.media-amazon.com/images/I/41uxuzLFDeL._AC_US600_.jpg</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>B0HKMPN41V</t>
+        </is>
+      </c>
+      <c r="M45" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装:消费性电子产品:电器:清洁机</t>
+        </is>
+      </c>
+      <c r="N45" s="12" t="inlineStr">
+        <is>
+          <t>家居、厨具、家装</t>
+        </is>
+      </c>
+      <c r="O45" s="13">
+        <v>17947</v>
+      </c>
+      <c r="P45" s="13"/>
+      <c r="Q45" s="14">
+        <v>0</v>
+      </c>
+      <c r="R45" s="15" t="inlineStr">
+        <is>
+          <t>电动清洗机\\\\清洁机</t>
+        </is>
+      </c>
+      <c r="S45" s="16" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="T45" s="13">
+        <v>8</v>
+      </c>
+      <c r="U45" s="14"/>
+      <c r="V45" s="13">
+        <v>75952</v>
+      </c>
+      <c r="W45" s="13"/>
+      <c r="X45" s="13"/>
+      <c r="Y45" s="17">
+        <v>2</v>
+      </c>
+      <c r="Z45" s="13">
+        <v>9494</v>
+      </c>
+      <c r="AA45" s="2"/>
+      <c r="AB45" s="1"/>
+      <c r="AC45" s="2"/>
+      <c r="AD45" s="17">
+        <v>29</v>
+      </c>
+      <c r="AE45" s="13">
+        <v>23</v>
+      </c>
+      <c r="AF45" s="18">
+        <v>5</v>
+      </c>
+      <c r="AG45" s="19">
+        <v>0</v>
+      </c>
+      <c r="AH45" s="13">
+        <v>675</v>
+      </c>
+      <c r="AI45" s="14">
+        <v>0.78</v>
+      </c>
+      <c r="AJ45"/>
+      <c r="AK45" s="11" t="inlineStr">
+        <is>
+          <t>2026-09-18</t>
+        </is>
+      </c>
+      <c r="AL45" s="17">
+        <v>10</v>
+      </c>
+      <c r="AM45" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AN45" s="11"/>
+      <c r="AO45" s="11"/>
+      <c r="AP45" s="2"/>
+      <c r="AQ45" s="17">
+        <v>10</v>
+      </c>
+      <c r="AR45" s="17">
+        <v>1</v>
+      </c>
+      <c r="AS45" s="12" t="inlineStr">
+        <is>
+          <t>caolidianpu</t>
+        </is>
+      </c>
+      <c r="AT45" s="11" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="AU45" s="11" t="inlineStr">
+        <is>
+          <t>CN</t>
+        </is>
+      </c>
+      <c r="AV45" s="12" t="inlineStr">
+        <is>
+          <t>guangdong 353400 CN</t>
+        </is>
+      </c>
+      <c r="AW45" s="11" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSFAH2380FVF</t>
+        </is>
+      </c>
+      <c r="AX45" s="11"/>
+      <c r="AY45" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="AZ45" s="11"/>
+      <c r="BA45" s="11"/>
+      <c r="BB45" s="11"/>
+      <c r="BC45" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BD45" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BE45" s="11"/>
+      <c r="BF45" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
+      <c r="BG45" s="11"/>
+      <c r="BH45" s="12"/>
+      <c r="BI45" s="20" t="inlineStr">
+        <is>
+          <t>亚马逊 精选</t>
+        </is>
+      </c>
+      <c r="BJ45" s="20" t="inlineStr">
+        <is>
+          <t>4.5 Kilograms</t>
+        </is>
+      </c>
+      <c r="BK45" s="20" t="inlineStr">
+        <is>
+          <t>4.50 kg</t>
+        </is>
+      </c>
+      <c r="BL45" s="20"/>
+      <c r="BM45" s="20"/>
+      <c r="BN45" s="20" t="inlineStr">
+        <is>
+          <t>4.5 kg</t>
+        </is>
+      </c>
+      <c r="BO45" s="20" t="inlineStr">
+        <is>
+          <t>4.50 kg</t>
+        </is>
+      </c>
+      <c r="BP45" s="20" t="inlineStr">
+        <is>
+          <t>52 x 28.5 x 18.5 cm</t>
+        </is>
+      </c>
+      <c r="BQ45" s="20" t="inlineStr">
+        <is>
+          <t>52.00 x 28.50 x 18.50 cm</t>
+        </is>
+      </c>
+      <c r="BR45" s="11" t="inlineStr">
+        <is>
+          <t>大件</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="24" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A46" s="11">
+        <v>45</v>
+      </c>
+      <c r="B46" s="11"/>
+      <c r="C46" s="12" t="inlineStr">
+        <is>
+          <t>B01BEH1OAC</t>
+        </is>
+      </c>
+      <c r="D46" s="12" t="inlineStr">
+        <is>
+          <t>颜色: 红色</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>品牌: H2O STEAMFX | 特殊功能: 高压力 | 随附部件: 排针喷嘴,清洁销,延长软管,擦拭工具,刮毛垫,衣物面料垫,尼龙刷 | 商品重量: 1560 克 | 油箱容积: 225 毫升</t>
+        </is>
+      </c>
+      <c r="F46" s="12" t="inlineStr">
+        <is>
+          <t>H2O STEAMFX</t>
+        </is>
+      </c>
+      <c r="G46" s="12" t="inlineStr">
+        <is>
+          <t>https://www.amazon.co.jp/-/zh/stores/%E3%83%80%E3%82%A4%E3%83%AC%E3%82%AF%E3%83%88%E3%83%86%E3%83%AC%E3%82%B7%E3%83%A7%E3%83%83%E3%83%97/page/5C9F3767-423D-4E02-98FC-726D8B2F56AE?lp_asin=B01BEH1OAC&amp;ref_=ast_bln</t>
+        </is>
+      </c>
+      <c r="H46" s="12" t="inlineStr">
+        <is>
+          <t>H2O 蒸汽FX 8件豪华套装(红色)</t>
+        </is>
+      </c>
+      <c r="I46" s="12" t="inlineStr">
+        <is>
+          <t>只需水，无需洗洁精，安心、经济。</t>
+        </is>
+      </c>
       <c r="J46" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0DRCGRJSR?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B01BEH1OAC?psc=1</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41wLqF+bzbL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/51cWEc-X2YL._AC_US600_.jpg</t>
         </is>
       </c>
       <c r="L46" s="12" t="inlineStr">
         <is>
-          <t>B0F486YKK4</t>
+          <t>B0151FQ7MI</t>
         </is>
       </c>
       <c r="M46" s="12" t="inlineStr">
@@ -19259,13 +19161,13 @@
         </is>
       </c>
       <c r="O46" s="13">
-        <v>30451</v>
+        <v>74982</v>
       </c>
       <c r="P46" s="13">
-        <v>65796</v>
+        <v>81811</v>
       </c>
       <c r="Q46" s="14">
-        <v>0.69</v>
+        <v>0.38</v>
       </c>
       <c r="R46" s="15" t="inlineStr">
         <is>
@@ -19274,17 +19176,15 @@
       </c>
       <c r="S46" s="16" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>50</t>
         </is>
       </c>
       <c r="T46" s="13">
-        <v>16</v>
-      </c>
-      <c r="U46" s="14">
-        <v>-0.97</v>
-      </c>
+        <v>17</v>
+      </c>
+      <c r="U46" s="14"/>
       <c r="V46" s="13">
-        <v>95680</v>
+        <v>74188</v>
       </c>
       <c r="W46" s="13"/>
       <c r="X46" s="13"/>
@@ -19292,38 +19192,32 @@
         <v>2</v>
       </c>
       <c r="Z46" s="13">
-        <v>5980</v>
+        <v>4364</v>
       </c>
       <c r="AA46" s="2"/>
       <c r="AB46" s="1"/>
-      <c r="AC46" s="2"/>
+      <c r="AC46" s="2">
+        <v>4</v>
+      </c>
       <c r="AD46" s="17">
-        <v>215</v>
+        <v>423</v>
       </c>
       <c r="AE46" s="13">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="AF46" s="18">
-        <v>4.1</v>
+        <v>3</v>
       </c>
       <c r="AG46" s="19">
-        <v>0.25</v>
-      </c>
-      <c r="AH46" s="13">
-        <v>472</v>
-      </c>
+        <v>0</v>
+      </c>
+      <c r="AH46" s="13"/>
       <c r="AI46" s="14">
-        <v>0.77</v>
+        <v>0</v>
       </c>
       <c r="AJ46"/>
-      <c r="AK46" s="11" t="inlineStr">
-        <is>
-          <t>2025-03-26</t>
-        </is>
-      </c>
-      <c r="AL46" s="17">
-        <v>551</v>
-      </c>
+      <c r="AK46" s="11"/>
+      <c r="AL46" s="17"/>
       <c r="AM46" s="11" t="inlineStr">
         <is>
           <t>NA</t>
@@ -19333,14 +19227,14 @@
       <c r="AO46" s="11"/>
       <c r="AP46" s="2"/>
       <c r="AQ46" s="17">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AR46" s="17">
-        <v>1</v>
+        <v>8</v>
       </c>
       <c r="AS46" s="12" t="inlineStr">
         <is>
-          <t>Megastar Store</t>
+          <t>ここclickで他品閲覧可能 安心対応ユウワン商事</t>
         </is>
       </c>
       <c r="AT46" s="11" t="inlineStr">
@@ -19350,17 +19244,17 @@
       </c>
       <c r="AU46" s="11" t="inlineStr">
         <is>
-          <t>CN</t>
+          <t>JP</t>
         </is>
       </c>
       <c r="AV46" s="12" t="inlineStr">
         <is>
-          <t>Zhejiang 310019 CN</t>
+          <t>神奈川県 2400025 JP</t>
         </is>
       </c>
       <c r="AW46" s="11" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES</t>
+          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JVN30QXJB2BN</t>
         </is>
       </c>
       <c r="AX46" s="11"/>
@@ -19373,65 +19267,33 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD46" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD46" s="11"/>
       <c r="BE46" s="11"/>
-      <c r="BF46" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF46" s="11"/>
       <c r="BG46" s="11"/>
       <c r="BH46" s="12"/>
       <c r="BI46" s="20"/>
       <c r="BJ46" s="20" t="inlineStr">
         <is>
-          <t>2.28 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK46" s="20" t="inlineStr">
-        <is>
-          <t>2.28 kg</t>
-        </is>
-      </c>
+          <t>1560 克</t>
+        </is>
+      </c>
+      <c r="BK46" s="20"/>
       <c r="BL46" s="20" t="inlineStr">
         <is>
-          <t>32.3 x 23.9 x 16.3 cm</t>
+          <t>20 x 11 x 21 cm</t>
         </is>
       </c>
       <c r="BM46" s="20" t="inlineStr">
         <is>
-          <t>32.30 x 23.90 x 16.30 cm</t>
-        </is>
-      </c>
-      <c r="BN46" s="20" t="inlineStr">
-        <is>
-          <t>2.28 kg</t>
-        </is>
-      </c>
-      <c r="BO46" s="20" t="inlineStr">
-        <is>
-          <t>2.28 kg</t>
-        </is>
-      </c>
-      <c r="BP46" s="20" t="inlineStr">
-        <is>
-          <t>32.3 x 23.9 x 16.3 cm</t>
-        </is>
-      </c>
-      <c r="BQ46" s="20" t="inlineStr">
-        <is>
-          <t>32.30 x 23.90 x 16.30 cm</t>
-        </is>
-      </c>
-      <c r="BR46" s="11" t="inlineStr">
-        <is>
-          <t>标准</t>
-        </is>
-      </c>
+          <t>20.00 x 11.00 x 21.00 cm</t>
+        </is>
+      </c>
+      <c r="BN46" s="20"/>
+      <c r="BO46" s="20"/>
+      <c r="BP46" s="20"/>
+      <c r="BQ46" s="20"/>
+      <c r="BR46" s="11"/>
     </row>
     <row r="47" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A47" s="11">
@@ -19440,56 +19302,52 @@
       <c r="B47" s="11"/>
       <c r="C47" s="12" t="inlineStr">
         <is>
-          <t>B0HK3489BN</t>
-        </is>
-      </c>
-      <c r="D47" s="12" t="inlineStr">
-        <is>
-          <t>颜色: yellow</t>
-        </is>
-      </c>
+          <t>B07GXPG63H</t>
+        </is>
+      </c>
+      <c r="D47" s="12"/>
       <c r="E47" s="12" t="inlineStr">
         <is>
-          <t>品牌: Waitbird | 特殊功能: 120℃の高温蒸気で 99.99% の細菌・ウイルスを除去、4.5Bar 高圧、1500W、ステンレス製ボイラー、角度調整可能なハンドル、21 点多機能アクセサリーセット、急速加熱、蒸気量調整機能、大容量水タンク、動作インジケーターランプ、洗剤不要クリーニング、チャイルドセーフティロック、高効率、時間短縮 | 推荐表面: サニタリー器具、床、タイル目地、ガラス面、シンク、シャワードア、トイレ、布張り家具、キッチンカウンター、コンロ、ソファ、カーテン、車内、カーシート、コーティング済み木製床、ラミネート床、ペット周り、カーペット、壁、窓、タイル、鏡、オーブン、BBQ グリル、シャワー室、浴槽、布地スチーム、ペットベッド、車内細部クリーニング | 随附部件: ナイロンブラシ4本、真鍮ブラシ2本、アイロンタオル3枚、マイクロファイバーモップパッド2枚、延長チューブ2本、計量カップ1個、手袋1個、アイロンブラシ1個、ストラップ1本、ガラスブラシ1個、大型ノズル1個、フロアブラシ1個、カーペットグライダー1個 | 油箱容积: 1100 毫升</t>
+          <t>品牌: KÄRCHER | 特殊功能: 高压力 | 推荐表面: 水槽 | 型号名称: KARCHER 清洁・除菌 蒸汽清洁器 SC2 EasyFix EasyFix 罐型 1.512-059.0 | 随附部件: Eezy Fix 地板喷嘴等</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
         <is>
-          <t>Waitbird</t>
+          <t>KÄRCHER</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/Waitbird/page/3EF06D38-11FF-4AB3-B913-B77B78E9E2C6?lp_asin=B0HK3489BN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto</t>
+          <t>https://www.amazon.co.jpnull</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>Waitbird ハンドスチームクリーナー 120℃高温蒸気除菌 4.5bar 高圧 21 点パーツ</t>
+          <t>Karcher 蒸汽清洁器 SC2 EasyFix 1.512-059.0 清扫/除菌</t>
         </is>
       </c>
       <c r="I47" s="12" t="inlineStr">
         <is>
-          <t>各任務のために21個の部品を完成する：ナイロン工具4個、黄銅工具2個、アイロン布3個、超微細繊維モップマット2個、延長管2本、計量カップ1個、手袋1個、アイロンブラシ1本、ベルト1本、ガラスブラシ1本、大ノズル1個、床ブラシ1本、カーペットキャリッジ1個、あらゆる表面に適用する。（注：スクロールボックスは個別に購入して、特定の要件を満たす必要があります。）
-安全第一、チャイルドロック付きと自動停止：統合チャイルドロックがあり、圧力が安全レベルを超えたり、水位が低くなったりすると、予期せぬ起動と自動停止を防ぐことができる。人間工学に適したハンドルは、長時間使用しても快適な操作を確保することができます。
-全面的な洗浄性能：Waitbirdは248°Fまでの高温蒸気を発生することができ、そして21個の多機能、交換可能な付属品を持ち、専門的に各種表面汚染物を洗浄し、徹底的な360°洗浄を実現し、盲点がない。これにより、ほとんどのアプリケーションシーンがカバーされます。
-38オンスの大水槽とインスタントスチームを使用して時間を節約：待ち時間が短く、清掃時間が長くなる：水は5分以内に248°Fに加熱し、持続的な高圧蒸気供給を提供して、あなたの水位に適応する（最大30オンス/900 mlを提案）。部屋全体を効率的に清潔にし、再充填の手間を最小限に。
-家、車の中、その他の場所での多用途：密封材の清掃、強化フローリング、家電製品、喫煙機、窓、自動車内装、ペットベッド、アウトドアグリル――家庭、車の所有者、ペットの所有者に非常に適している。化学物質のない生活様式の環境保護ソリューション</t>
+          <t>清洁面积（水箱装满水时可清洁的面积）（平方米）：75 加热功率（W）：1500
+蒸汽吐出压力(MPa):0.32 电源线(m):4
+加热时间(分钟):6.5 锅炉水箱容量(升):1
+电源(Ph/V/Hz):1/100/50-60 主体质量(不含配件)(kg):2.9
+包装重量(kg):5 尺寸(长×宽×高)(毫米):380 x 254 x 260</t>
         </is>
       </c>
       <c r="J47" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B0HK3489BN?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B07GXPG63H?psc=1</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41uxuzLFDeL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41H+7reLbSL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L47" s="12" t="inlineStr">
         <is>
-          <t>B0HKMPN41V</t>
+          <t>B07GXPG63H</t>
         </is>
       </c>
       <c r="M47" s="12" t="inlineStr">
@@ -19503,7 +19361,7 @@
         </is>
       </c>
       <c r="O47" s="13">
-        <v>17947</v>
+        <v>52967</v>
       </c>
       <c r="P47" s="13"/>
       <c r="Q47" s="14">
@@ -19516,54 +19374,38 @@
       </c>
       <c r="S47" s="16" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="T47" s="13">
-        <v>8</v>
-      </c>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="T47" s="13"/>
       <c r="U47" s="14"/>
-      <c r="V47" s="13">
-        <v>75952</v>
-      </c>
+      <c r="V47" s="13"/>
       <c r="W47" s="13"/>
       <c r="X47" s="13"/>
       <c r="Y47" s="17">
-        <v>2</v>
-      </c>
-      <c r="Z47" s="13">
-        <v>9494</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="Z47" s="13"/>
       <c r="AA47" s="2"/>
       <c r="AB47" s="1"/>
       <c r="AC47" s="2"/>
       <c r="AD47" s="17">
-        <v>29</v>
-      </c>
-      <c r="AE47" s="13">
-        <v>23</v>
-      </c>
+        <v>606</v>
+      </c>
+      <c r="AE47" s="13"/>
       <c r="AF47" s="18">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AG47" s="19">
         <v>0</v>
       </c>
-      <c r="AH47" s="13">
-        <v>675</v>
-      </c>
+      <c r="AH47" s="13"/>
       <c r="AI47" s="14">
-        <v>0.78</v>
+        <v>0</v>
       </c>
       <c r="AJ47"/>
-      <c r="AK47" s="11" t="inlineStr">
-        <is>
-          <t>2026-09-18</t>
-        </is>
-      </c>
-      <c r="AL47" s="17">
-        <v>10</v>
-      </c>
+      <c r="AK47" s="11"/>
+      <c r="AL47" s="17"/>
       <c r="AM47" s="11" t="inlineStr">
         <is>
           <t>NA</t>
@@ -19572,37 +19414,17 @@
       <c r="AN47" s="11"/>
       <c r="AO47" s="11"/>
       <c r="AP47" s="2"/>
-      <c r="AQ47" s="17">
-        <v>10</v>
-      </c>
-      <c r="AR47" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS47" s="12" t="inlineStr">
-        <is>
-          <t>caolidianpu</t>
-        </is>
-      </c>
+      <c r="AQ47" s="17"/>
+      <c r="AR47" s="17"/>
+      <c r="AS47" s="12"/>
       <c r="AT47" s="11" t="inlineStr">
         <is>
           <t>NA</t>
         </is>
       </c>
-      <c r="AU47" s="11" t="inlineStr">
-        <is>
-          <t>CN</t>
-        </is>
-      </c>
-      <c r="AV47" s="12" t="inlineStr">
-        <is>
-          <t>guangdong 353400 CN</t>
-        </is>
-      </c>
-      <c r="AW47" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSFAH2380FVF</t>
-        </is>
-      </c>
+      <c r="AU47" s="11"/>
+      <c r="AV47" s="12"/>
+      <c r="AW47" s="11"/>
       <c r="AX47" s="11"/>
       <c r="AY47" s="11" t="inlineStr">
         <is>
@@ -19617,11 +19439,7 @@
           <t>Y</t>
         </is>
       </c>
-      <c r="BD47" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BD47" s="11"/>
       <c r="BE47" s="11"/>
       <c r="BF47" s="11" t="inlineStr">
         <is>
@@ -19637,41 +19455,17 @@
       </c>
       <c r="BJ47" s="20" t="inlineStr">
         <is>
-          <t>4.5 Kilograms</t>
-        </is>
-      </c>
-      <c r="BK47" s="20" t="inlineStr">
-        <is>
-          <t>4.50 kg</t>
-        </is>
-      </c>
+          <t>4455 克</t>
+        </is>
+      </c>
+      <c r="BK47" s="20"/>
       <c r="BL47" s="20"/>
       <c r="BM47" s="20"/>
-      <c r="BN47" s="20" t="inlineStr">
-        <is>
-          <t>4.5 kg</t>
-        </is>
-      </c>
-      <c r="BO47" s="20" t="inlineStr">
-        <is>
-          <t>4.50 kg</t>
-        </is>
-      </c>
-      <c r="BP47" s="20" t="inlineStr">
-        <is>
-          <t>52 x 28.5 x 18.5 cm</t>
-        </is>
-      </c>
-      <c r="BQ47" s="20" t="inlineStr">
-        <is>
-          <t>52.00 x 28.50 x 18.50 cm</t>
-        </is>
-      </c>
-      <c r="BR47" s="11" t="inlineStr">
-        <is>
-          <t>大件</t>
-        </is>
-      </c>
+      <c r="BN47" s="20"/>
+      <c r="BO47" s="20"/>
+      <c r="BP47" s="20"/>
+      <c r="BQ47" s="20"/>
+      <c r="BR47" s="11"/>
     </row>
     <row r="48" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="11">
@@ -19680,52 +19474,56 @@
       <c r="B48" s="11"/>
       <c r="C48" s="12" t="inlineStr">
         <is>
-          <t>B01BEH1OAC</t>
+          <t>B0CZ3YBX8C</t>
         </is>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
-          <t>颜色: 红色</t>
+          <t>样式: 02.连续供水、家庭清洁(SC3)</t>
         </is>
       </c>
       <c r="E48" s="12" t="inlineStr">
         <is>
-          <t>品牌: H2O STEAMFX | 特殊功能: 高压力 | 随附部件: 排针喷嘴,清洁销,延长软管,擦拭工具,刮毛垫,衣物面料垫,尼龙刷 | 商品重量: 1560 克 | 油箱容积: 225 毫升</t>
+          <t>品牌: KÄRCHER | 特殊功能: Easy fix 地板吸嘴、蒸汽锁定功能 | 型号名称: SC 3 EasyFix W | 随附部件: 管子・Easy fix地板吸嘴・手刷・喷嘴・刷子黑・刷子黄・超细纤维制布・超细纤维制盖・除比例滤芯 ・使用说明书 | 瓦数: 1500 瓦特</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
         <is>
-          <t>H2O STEAMFX</t>
+          <t>KÄRCHER</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/-/zh/stores/%E3%83%80%E3%82%A4%E3%83%AC%E3%82%AF%E3%83%88%E3%83%86%E3%83%AC%E3%82%B7%E3%83%A7%E3%83%83%E3%83%97/page/5C9F3767-423D-4E02-98FC-726D8B2F56AE?lp_asin=B01BEH1OAC&amp;ref_=ast_bln</t>
+          <t>https://www.amazon.co.jpnull</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>H2O 蒸汽FX 8件豪华套装(红色)</t>
+          <t>【24年新発売】 ケルヒャー(Karcher) スチームクリーナー SC3 EasyFix W 连续供水可能型号 约40秒即可加热完成的流动加热器加热 能浮起顽固污渍 仅用水进行除菌消臭 地板清洁 油污 地毯 干净地板 水垢 厨房 浴室 玄关 厕所 车 衣物 配件齐全 选配配件也很丰富 1.513-655.0</t>
         </is>
       </c>
       <c r="I48" s="12" t="inlineStr">
         <is>
-          <t>只需水，无需洗洁精，安心、经济。</t>
+          <t>【产品介绍】蒸汽清洁器通过高温蒸汽“浮起顽固污垢并将其去除”，仅用水即可“消毒并去除病毒、细菌和螨虫”。 (※详情请查看卡赫官方HP)
+【蒸汽清洁器的有效使用方法】等蒸汽稳定后再安装墙布等，可以减少墙布的湿润，加快地面等的干燥。
+推荐以下人士:希望在家里每个角落都漂亮的人士。 想要休息日一起打扫的人士。 对于关心厨房周围油污的人、经常进行地板清洁的人、有宠物或孩子的家庭、赤脚生活的人、经常炸食物的人。 【产品特点】加热（等待时间）约35秒，通过供水可连续使用。
+【配件】管道・易固定地板喷嘴・手刷・喷嘴头・黑色刷子・黄色刷子・微纤维擦布・微纤维盖套・除垢碳酸钙盒・使用说明书【推荐附件】地毯滑轮、"Kercher官方"擦布。
+【加热时间(秒)】约35。 【锅炉水箱容量(升)】1。 【蒸汽出水压力(MPa)】0.35。 【产品尺寸 (厘米)】36 x 25.3 x 23.6。 【产品重量(不含配件)(kg)】3.1 。</t>
         </is>
       </c>
       <c r="J48" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B01BEH1OAC?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0CZ3YBX8C?psc=1</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/51cWEc-X2YL._AC_US600_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/31nhFm22HvL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L48" s="12" t="inlineStr">
         <is>
-          <t>B0151FQ7MI</t>
+          <t>B0F5W9SGVC</t>
         </is>
       </c>
       <c r="M48" s="12" t="inlineStr">
@@ -19739,13 +19537,11 @@
         </is>
       </c>
       <c r="O48" s="13">
-        <v>74982</v>
-      </c>
-      <c r="P48" s="13">
-        <v>81811</v>
-      </c>
+        <v>12377</v>
+      </c>
+      <c r="P48" s="13"/>
       <c r="Q48" s="14">
-        <v>0.38</v>
+        <v>0</v>
       </c>
       <c r="R48" s="15" t="inlineStr">
         <is>
@@ -19754,37 +19550,33 @@
       </c>
       <c r="S48" s="16" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="T48" s="13">
-        <v>17</v>
-      </c>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="T48" s="13"/>
       <c r="U48" s="14"/>
-      <c r="V48" s="13">
-        <v>74188</v>
-      </c>
-      <c r="W48" s="13"/>
+      <c r="V48" s="13"/>
+      <c r="W48" s="13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
       <c r="X48" s="13"/>
       <c r="Y48" s="17">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Z48" s="13">
-        <v>4364</v>
+        <v>205</v>
       </c>
       <c r="AA48" s="2"/>
       <c r="AB48" s="1"/>
-      <c r="AC48" s="2">
-        <v>4</v>
-      </c>
+      <c r="AC48" s="2"/>
       <c r="AD48" s="17">
-        <v>423</v>
-      </c>
-      <c r="AE48" s="13">
-        <v>0</v>
-      </c>
+        <v>69</v>
+      </c>
+      <c r="AE48" s="13"/>
       <c r="AF48" s="18">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="AG48" s="19">
         <v>0</v>
@@ -19798,75 +19590,63 @@
       <c r="AL48" s="17"/>
       <c r="AM48" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN48" s="11"/>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AN48" s="11" t="inlineStr">
+        <is>
+          <t>11天</t>
+        </is>
+      </c>
       <c r="AO48" s="11"/>
-      <c r="AP48" s="2"/>
-      <c r="AQ48" s="17">
-        <v>7</v>
-      </c>
+      <c r="AP48" s="2">
+        <v>88</v>
+      </c>
+      <c r="AQ48" s="17"/>
       <c r="AR48" s="17">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="AS48" s="12" t="inlineStr">
         <is>
-          <t>ここclickで他品閲覧可能 安心対応ユウワン商事</t>
+          <t>Amazon</t>
         </is>
       </c>
       <c r="AT48" s="11" t="inlineStr">
         <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU48" s="11" t="inlineStr">
-        <is>
-          <t>JP</t>
-        </is>
-      </c>
-      <c r="AV48" s="12" t="inlineStr">
-        <is>
-          <t>神奈川県 2400025 JP</t>
-        </is>
-      </c>
-      <c r="AW48" s="11" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JVN30QXJB2BN</t>
-        </is>
-      </c>
+          <t>AMZ</t>
+        </is>
+      </c>
+      <c r="AU48" s="11"/>
+      <c r="AV48" s="12"/>
+      <c r="AW48" s="11"/>
       <c r="AX48" s="11"/>
       <c r="AY48" s="11"/>
       <c r="AZ48" s="11"/>
       <c r="BA48" s="11"/>
       <c r="BB48" s="11"/>
-      <c r="BC48" s="11" t="inlineStr">
+      <c r="BC48" s="11"/>
+      <c r="BD48" s="11" t="inlineStr">
         <is>
           <t>Y</t>
         </is>
       </c>
-      <c r="BD48" s="11"/>
       <c r="BE48" s="11"/>
-      <c r="BF48" s="11"/>
+      <c r="BF48" s="11" t="inlineStr">
+        <is>
+          <t>Y</t>
+        </is>
+      </c>
       <c r="BG48" s="11"/>
       <c r="BH48" s="12"/>
       <c r="BI48" s="20"/>
       <c r="BJ48" s="20" t="inlineStr">
         <is>
-          <t>1560 克</t>
+          <t>3.1 千克</t>
         </is>
       </c>
       <c r="BK48" s="20"/>
-      <c r="BL48" s="20" t="inlineStr">
-        <is>
-          <t>20 x 11 x 21 cm</t>
-        </is>
-      </c>
-      <c r="BM48" s="20" t="inlineStr">
-        <is>
-          <t>20.00 x 11.00 x 21.00 cm</t>
-        </is>
-      </c>
+      <c r="BL48" s="20"/>
+      <c r="BM48" s="20"/>
       <c r="BN48" s="20"/>
       <c r="BO48" s="20"/>
       <c r="BP48" s="20"/>
@@ -19880,52 +19660,58 @@
       <c r="B49" s="11"/>
       <c r="C49" s="12" t="inlineStr">
         <is>
-          <t>B07GXPG63H</t>
-        </is>
-      </c>
-      <c r="D49" s="12"/>
+          <t>B0HKBW4BLR</t>
+        </is>
+      </c>
+      <c r="D49" s="12" t="inlineStr">
+        <is>
+          <t>Set name: 附带2个专用清洗液。</t>
+        </is>
+      </c>
       <c r="E49" s="12" t="inlineStr">
         <is>
-          <t>品牌: KÄRCHER | 特殊功能: 高压力 | 推荐表面: 水槽 | 型号名称: KARCHER 清洁・除菌 蒸汽清洁器 SC2 EasyFix EasyFix 罐型 1.512-059.0 | 随附部件: Eezy Fix 地板喷嘴等</t>
+          <t>品牌: Bissell | 颜色: 蓝色 | 型号名称: 4065P-4310P | 制造商: BISSELL | 商品数量: 1</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
         <is>
-          <t>KÄRCHER</t>
+          <t>Bissell</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jpnull</t>
+          <t>https://www.amazon.co.jp/-/zh/Bissell/b/ref=bl_dp_s_web_220431009051?ie=UTF8&amp;node=220431009051&amp;field-lbr_brands_browse-bin=Bissell</t>
         </is>
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>Karcher 蒸汽清洁器 SC2 EasyFix 1.512-059.0 清扫/除菌</t>
+          <t>BISSELL [Wahei freiz 和平] SpotClean™ Mini Pet Cordless (地毯、布制家具用) 附带2个专用清洗液</t>
         </is>
       </c>
       <c r="I49" s="12" t="inlineStr">
         <is>
-          <t>清洁面积（水箱装满水时可清洁的面积）（平方米）：75 加热功率（W）：1500
-蒸汽吐出压力(MPa):0.32 电源线(m):4
-加热时间(分钟):6.5 锅炉水箱容量(升):1
-电源(Ph/V/Hz):1/100/50-60 主体质量(不含配件)(kg):2.9
-包装重量(kg):5 尺寸(长×宽×高)(毫米):380 x 254 x 260</t>
+          <t>[宠物的粗相、雨天泥后,在现场清洗] 在沙发上起床的宠物的粗相、雨天散步回家后还有泥泞的脚印。 即使要清洁,沙发、地毯和地毯也不能直接放入洗衣机清洗。 "SpotClean Mini Pet Cordless"是一款在想要清洗但无法简单清洗"的布制品的污垢中,喷出水和专用清洗液,用刷子漂浮污垢,吸去污垢和水分的无线冲洗清洁器。
+【喷洒、轻揉、吸附的3步】用温水(60度以内)和专用清洗液喷到污垢,用刷子浮起纤维污垢,吸收污垢和水分。 采用2水箱方式,可将清水0.5升和0.4升污水分开,不会与干净的水混合。 由于吸出的水会积聚在污水箱中,所以一眼就能确认平时擦拭难以到达的污垢的同时,可以直接清洗脏的场所。
+【约2.85千克、用途可选的2种运行模式】连续高吸力的标准模式最长可使用约15分钟、BatteryBoost+(节能模式)最长可使用约20分钟。 充电时间约为4小时。 BatteryBoost+(节能模式)是一种省电设计,当工具接触清洁表面时,吸力会增加,松开时电机处于空闲状态。 ※最长约 20 分钟是接触所有使用时间的53%作为参考。 根据使用条件和电池状态而变化。
+【从地毯、宠物床到汽车座椅】每天使用的地毯和宠物床,虽然积累了毛发和皮脂等各种污垢,但根据大小和材料的不同,可能会出现难以整体清洗的情况。 只需清洗所需部分,吸收污垢和水分。 无线设计,不仅可以在家里携带,也可以在车内使用。 适用于沙发、地毯、地毯、宠物床、布制汽车座椅等,与宠物共生的各种场所。 在食物或饮料洒出来时,也可用于不来自宠物的日常布制品的污渍。
+[为与宠物生活家庭设计的专用清洁液] 配有不含香料和色素的专用清洁液"Free &amp; Clear Pet Formula"。 BISSELL的目标是不仅使表面看起来漂亮。 通过将水和清洗液漂浮在布纤维中的污垢并吸收,从而去除造成异味的污垢。
+[基于500小时以上的测试的"Pet Proven"]基于BISSELL的"Pet Proven"标准,考虑到实际宠物的污垢,在实验室和家庭均进行测试。 Pet Proven产品包括开发、清洁测试、家庭测试等,共计500小时以上的测试。 Pet Proven ― Lab Tested. Life Approved.
+[可见污垢的吸水罐] 采用透明的污水箱,可以看到吸入的污水。 在清洗沙发和地毯后,看着吸出的水,会注意到"太脏了"。 不仅有明显的斑点,还要定期清洗布制品本身。 BISSELL日本,像"吸尘器一样,清洗布制品。 提出了""的全新家庭清洁习惯。 BISSELL1876年诞生于美国密歇根州,2026年迎来150周年的家居清洁品牌。</t>
         </is>
       </c>
       <c r="J49" s="12" t="inlineStr">
         <is>
-          <t>https://www.amazon.co.jp/dp/B07GXPG63H?psc=1</t>
+          <t>https://www.amazon.co.jp/dp/B0HKBW4BLR?psc=1</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
         <is>
-          <t>https://m.media-amazon.com/images/I/41H+7reLbSL._AC_US200_.jpg</t>
+          <t>https://m.media-amazon.com/images/I/41Pe+u97axL._AC_US200_.jpg</t>
         </is>
       </c>
       <c r="L49" s="12" t="inlineStr">
         <is>
-          <t>B07GXPG63H</t>
+          <t>B0HKD7LVQY</t>
         </is>
       </c>
       <c r="M49" s="12" t="inlineStr">
@@ -19939,7 +19725,7 @@
         </is>
       </c>
       <c r="O49" s="13">
-        <v>52967</v>
+        <v>57574</v>
       </c>
       <c r="P49" s="13"/>
       <c r="Q49" s="14">
@@ -19952,7 +19738,7 @@
       </c>
       <c r="S49" s="16" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>41</t>
         </is>
       </c>
       <c r="T49" s="13"/>
@@ -19961,18 +19747,18 @@
       <c r="W49" s="13"/>
       <c r="X49" s="13"/>
       <c r="Y49" s="17">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="Z49" s="13"/>
       <c r="AA49" s="2"/>
       <c r="AB49" s="1"/>
       <c r="AC49" s="2"/>
       <c r="AD49" s="17">
-        <v>606</v>
+        <v>7</v>
       </c>
       <c r="AE49" s="13"/>
       <c r="AF49" s="18">
-        <v>4</v>
+        <v>4.6</v>
       </c>
       <c r="AG49" s="19">
         <v>0</v>
@@ -20004,38 +19790,18 @@
       <c r="AV49" s="12"/>
       <c r="AW49" s="11"/>
       <c r="AX49" s="11"/>
-      <c r="AY49" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="AY49" s="11"/>
       <c r="AZ49" s="11"/>
       <c r="BA49" s="11"/>
       <c r="BB49" s="11"/>
-      <c r="BC49" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BC49" s="11"/>
       <c r="BD49" s="11"/>
       <c r="BE49" s="11"/>
-      <c r="BF49" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
+      <c r="BF49" s="11"/>
       <c r="BG49" s="11"/>
       <c r="BH49" s="12"/>
-      <c r="BI49" s="20" t="inlineStr">
-        <is>
-          <t>亚马逊 精选</t>
-        </is>
-      </c>
-      <c r="BJ49" s="20" t="inlineStr">
-        <is>
-          <t>4455 克</t>
-        </is>
-      </c>
+      <c r="BI49" s="20"/>
+      <c r="BJ49" s="20"/>
       <c r="BK49" s="20"/>
       <c r="BL49" s="20"/>
       <c r="BM49" s="20"/>
@@ -20044,350 +19810,6 @@
       <c r="BP49" s="20"/>
       <c r="BQ49" s="20"/>
       <c r="BR49" s="11"/>
-    </row>
-    <row r="50" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="11">
-        <v>49</v>
-      </c>
-      <c r="B50" s="11"/>
-      <c r="C50" s="12" t="inlineStr">
-        <is>
-          <t>B0CZ3YBX8C</t>
-        </is>
-      </c>
-      <c r="D50" s="12" t="inlineStr">
-        <is>
-          <t>样式: 02.连续供水、家庭清洁(SC3)</t>
-        </is>
-      </c>
-      <c r="E50" s="12" t="inlineStr">
-        <is>
-          <t>品牌: KÄRCHER | 特殊功能: Easy fix 地板吸嘴、蒸汽锁定功能 | 型号名称: SC 3 EasyFix W | 随附部件: 管子・Easy fix地板吸嘴・手刷・喷嘴・刷子黑・刷子黄・超细纤维制布・超细纤维制盖・除比例滤芯 ・使用说明书 | 瓦数: 1500 瓦特</t>
-        </is>
-      </c>
-      <c r="F50" s="12" t="inlineStr">
-        <is>
-          <t>KÄRCHER</t>
-        </is>
-      </c>
-      <c r="G50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jpnull</t>
-        </is>
-      </c>
-      <c r="H50" s="12" t="inlineStr">
-        <is>
-          <t>【24年新発売】 ケルヒャー(Karcher) スチームクリーナー SC3 EasyFix W 连续供水可能型号 约40秒即可加热完成的流动加热器加热 能浮起顽固污渍 仅用水进行除菌消臭 地板清洁 油污 地毯 干净地板 水垢 厨房 浴室 玄关 厕所 车 衣物 配件齐全 选配配件也很丰富 1.513-655.0</t>
-        </is>
-      </c>
-      <c r="I50" s="12" t="inlineStr">
-        <is>
-          <t>【产品介绍】蒸汽清洁器通过高温蒸汽“浮起顽固污垢并将其去除”，仅用水即可“消毒并去除病毒、细菌和螨虫”。 (※详情请查看卡赫官方HP)
-【蒸汽清洁器的有效使用方法】等蒸汽稳定后再安装墙布等，可以减少墙布的湿润，加快地面等的干燥。
-推荐以下人士:希望在家里每个角落都漂亮的人士。 想要休息日一起打扫的人士。 对于关心厨房周围油污的人、经常进行地板清洁的人、有宠物或孩子的家庭、赤脚生活的人、经常炸食物的人。 【产品特点】加热（等待时间）约35秒，通过供水可连续使用。
-【配件】管道・易固定地板喷嘴・手刷・喷嘴头・黑色刷子・黄色刷子・微纤维擦布・微纤维盖套・除垢碳酸钙盒・使用说明书【推荐附件】地毯滑轮、"Kercher官方"擦布。
-【加热时间(秒)】约35。 【锅炉水箱容量(升)】1。 【蒸汽出水压力(MPa)】0.35。 【产品尺寸 (厘米)】36 x 25.3 x 23.6。 【产品重量(不含配件)(kg)】3.1 。</t>
-        </is>
-      </c>
-      <c r="J50" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0CZ3YBX8C?psc=1</t>
-        </is>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/31nhFm22HvL._AC_US200_.jpg</t>
-        </is>
-      </c>
-      <c r="L50" s="12" t="inlineStr">
-        <is>
-          <t>B0F5W9SGVC</t>
-        </is>
-      </c>
-      <c r="M50" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:清洁机</t>
-        </is>
-      </c>
-      <c r="N50" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O50" s="13">
-        <v>12377</v>
-      </c>
-      <c r="P50" s="13"/>
-      <c r="Q50" s="14">
-        <v>0</v>
-      </c>
-      <c r="R50" s="15" t="inlineStr">
-        <is>
-          <t>电动清洗机\\\\清洁机</t>
-        </is>
-      </c>
-      <c r="S50" s="16" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="T50" s="13"/>
-      <c r="U50" s="14"/>
-      <c r="V50" s="13"/>
-      <c r="W50" s="13" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="X50" s="13"/>
-      <c r="Y50" s="17">
-        <v>4</v>
-      </c>
-      <c r="Z50" s="13">
-        <v>205</v>
-      </c>
-      <c r="AA50" s="2"/>
-      <c r="AB50" s="1"/>
-      <c r="AC50" s="2"/>
-      <c r="AD50" s="17">
-        <v>69</v>
-      </c>
-      <c r="AE50" s="13"/>
-      <c r="AF50" s="18">
-        <v>3.9</v>
-      </c>
-      <c r="AG50" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH50" s="13"/>
-      <c r="AI50" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ50"/>
-      <c r="AK50" s="11"/>
-      <c r="AL50" s="17"/>
-      <c r="AM50" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AN50" s="11" t="inlineStr">
-        <is>
-          <t>11天</t>
-        </is>
-      </c>
-      <c r="AO50" s="11"/>
-      <c r="AP50" s="2">
-        <v>88</v>
-      </c>
-      <c r="AQ50" s="17"/>
-      <c r="AR50" s="17">
-        <v>1</v>
-      </c>
-      <c r="AS50" s="12" t="inlineStr">
-        <is>
-          <t>Amazon</t>
-        </is>
-      </c>
-      <c r="AT50" s="11" t="inlineStr">
-        <is>
-          <t>AMZ</t>
-        </is>
-      </c>
-      <c r="AU50" s="11"/>
-      <c r="AV50" s="12"/>
-      <c r="AW50" s="11"/>
-      <c r="AX50" s="11"/>
-      <c r="AY50" s="11"/>
-      <c r="AZ50" s="11"/>
-      <c r="BA50" s="11"/>
-      <c r="BB50" s="11"/>
-      <c r="BC50" s="11"/>
-      <c r="BD50" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BE50" s="11"/>
-      <c r="BF50" s="11" t="inlineStr">
-        <is>
-          <t>Y</t>
-        </is>
-      </c>
-      <c r="BG50" s="11"/>
-      <c r="BH50" s="12"/>
-      <c r="BI50" s="20"/>
-      <c r="BJ50" s="20" t="inlineStr">
-        <is>
-          <t>3.1 千克</t>
-        </is>
-      </c>
-      <c r="BK50" s="20"/>
-      <c r="BL50" s="20"/>
-      <c r="BM50" s="20"/>
-      <c r="BN50" s="20"/>
-      <c r="BO50" s="20"/>
-      <c r="BP50" s="20"/>
-      <c r="BQ50" s="20"/>
-      <c r="BR50" s="11"/>
-    </row>
-    <row r="51" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="11">
-        <v>50</v>
-      </c>
-      <c r="B51" s="11"/>
-      <c r="C51" s="12" t="inlineStr">
-        <is>
-          <t>B0HKBW4BLR</t>
-        </is>
-      </c>
-      <c r="D51" s="12" t="inlineStr">
-        <is>
-          <t>Set name: 附带2个专用清洗液。</t>
-        </is>
-      </c>
-      <c r="E51" s="12" t="inlineStr">
-        <is>
-          <t>品牌: Bissell | 颜色: 蓝色 | 型号名称: 4065P-4310P | 制造商: BISSELL | 商品数量: 1</t>
-        </is>
-      </c>
-      <c r="F51" s="12" t="inlineStr">
-        <is>
-          <t>Bissell</t>
-        </is>
-      </c>
-      <c r="G51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/-/zh/Bissell/b/ref=bl_dp_s_web_220431009051?ie=UTF8&amp;node=220431009051&amp;field-lbr_brands_browse-bin=Bissell</t>
-        </is>
-      </c>
-      <c r="H51" s="12" t="inlineStr">
-        <is>
-          <t>BISSELL [Wahei freiz 和平] SpotClean™ Mini Pet Cordless (地毯、布制家具用) 附带2个专用清洗液</t>
-        </is>
-      </c>
-      <c r="I51" s="12" t="inlineStr">
-        <is>
-          <t>[宠物的粗相、雨天泥后,在现场清洗] 在沙发上起床的宠物的粗相、雨天散步回家后还有泥泞的脚印。 即使要清洁,沙发、地毯和地毯也不能直接放入洗衣机清洗。 "SpotClean Mini Pet Cordless"是一款在想要清洗但无法简单清洗"的布制品的污垢中,喷出水和专用清洗液,用刷子漂浮污垢,吸去污垢和水分的无线冲洗清洁器。
-【喷洒、轻揉、吸附的3步】用温水(60度以内)和专用清洗液喷到污垢,用刷子浮起纤维污垢,吸收污垢和水分。 采用2水箱方式,可将清水0.5升和0.4升污水分开,不会与干净的水混合。 由于吸出的水会积聚在污水箱中,所以一眼就能确认平时擦拭难以到达的污垢的同时,可以直接清洗脏的场所。
-【约2.85千克、用途可选的2种运行模式】连续高吸力的标准模式最长可使用约15分钟、BatteryBoost+(节能模式)最长可使用约20分钟。 充电时间约为4小时。 BatteryBoost+(节能模式)是一种省电设计,当工具接触清洁表面时,吸力会增加,松开时电机处于空闲状态。 ※最长约 20 分钟是接触所有使用时间的53%作为参考。 根据使用条件和电池状态而变化。
-【从地毯、宠物床到汽车座椅】每天使用的地毯和宠物床,虽然积累了毛发和皮脂等各种污垢,但根据大小和材料的不同,可能会出现难以整体清洗的情况。 只需清洗所需部分,吸收污垢和水分。 无线设计,不仅可以在家里携带,也可以在车内使用。 适用于沙发、地毯、地毯、宠物床、布制汽车座椅等,与宠物共生的各种场所。 在食物或饮料洒出来时,也可用于不来自宠物的日常布制品的污渍。
-[为与宠物生活家庭设计的专用清洁液] 配有不含香料和色素的专用清洁液"Free &amp; Clear Pet Formula"。 BISSELL的目标是不仅使表面看起来漂亮。 通过将水和清洗液漂浮在布纤维中的污垢并吸收,从而去除造成异味的污垢。
-[基于500小时以上的测试的"Pet Proven"]基于BISSELL的"Pet Proven"标准,考虑到实际宠物的污垢,在实验室和家庭均进行测试。 Pet Proven产品包括开发、清洁测试、家庭测试等,共计500小时以上的测试。 Pet Proven ― Lab Tested. Life Approved.
-[可见污垢的吸水罐] 采用透明的污水箱,可以看到吸入的污水。 在清洗沙发和地毯后,看着吸出的水,会注意到"太脏了"。 不仅有明显的斑点,还要定期清洗布制品本身。 BISSELL日本,像"吸尘器一样,清洗布制品。 提出了""的全新家庭清洁习惯。 BISSELL1876年诞生于美国密歇根州,2026年迎来150周年的家居清洁品牌。</t>
-        </is>
-      </c>
-      <c r="J51" s="12" t="inlineStr">
-        <is>
-          <t>https://www.amazon.co.jp/dp/B0HKBW4BLR?psc=1</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
-        <is>
-          <t>https://m.media-amazon.com/images/I/41Pe+u97axL._AC_US200_.jpg</t>
-        </is>
-      </c>
-      <c r="L51" s="12" t="inlineStr">
-        <is>
-          <t>B0HKD7LVQY</t>
-        </is>
-      </c>
-      <c r="M51" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装:消费性电子产品:电器:清洁机</t>
-        </is>
-      </c>
-      <c r="N51" s="12" t="inlineStr">
-        <is>
-          <t>家居、厨具、家装</t>
-        </is>
-      </c>
-      <c r="O51" s="13">
-        <v>57574</v>
-      </c>
-      <c r="P51" s="13"/>
-      <c r="Q51" s="14">
-        <v>0</v>
-      </c>
-      <c r="R51" s="15" t="inlineStr">
-        <is>
-          <t>电动清洗机\\\\清洁机</t>
-        </is>
-      </c>
-      <c r="S51" s="16" t="inlineStr">
-        <is>
-          <t>41</t>
-        </is>
-      </c>
-      <c r="T51" s="13"/>
-      <c r="U51" s="14"/>
-      <c r="V51" s="13"/>
-      <c r="W51" s="13"/>
-      <c r="X51" s="13"/>
-      <c r="Y51" s="17">
-        <v>2</v>
-      </c>
-      <c r="Z51" s="13"/>
-      <c r="AA51" s="2"/>
-      <c r="AB51" s="1"/>
-      <c r="AC51" s="2"/>
-      <c r="AD51" s="17">
-        <v>7</v>
-      </c>
-      <c r="AE51" s="13"/>
-      <c r="AF51" s="18">
-        <v>4.6</v>
-      </c>
-      <c r="AG51" s="19">
-        <v>0</v>
-      </c>
-      <c r="AH51" s="13"/>
-      <c r="AI51" s="14">
-        <v>0</v>
-      </c>
-      <c r="AJ51"/>
-      <c r="AK51" s="11"/>
-      <c r="AL51" s="17"/>
-      <c r="AM51" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AN51" s="11"/>
-      <c r="AO51" s="11"/>
-      <c r="AP51" s="2"/>
-      <c r="AQ51" s="17"/>
-      <c r="AR51" s="17"/>
-      <c r="AS51" s="12"/>
-      <c r="AT51" s="11" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="AU51" s="11"/>
-      <c r="AV51" s="12"/>
-      <c r="AW51" s="11"/>
-      <c r="AX51" s="11"/>
-      <c r="AY51" s="11"/>
-      <c r="AZ51" s="11"/>
-      <c r="BA51" s="11"/>
-      <c r="BB51" s="11"/>
-      <c r="BC51" s="11"/>
-      <c r="BD51" s="11"/>
-      <c r="BE51" s="11"/>
-      <c r="BF51" s="11"/>
-      <c r="BG51" s="11"/>
-      <c r="BH51" s="12"/>
-      <c r="BI51" s="20"/>
-      <c r="BJ51" s="20"/>
-      <c r="BK51" s="20"/>
-      <c r="BL51" s="20"/>
-      <c r="BM51" s="20"/>
-      <c r="BN51" s="20"/>
-      <c r="BO51" s="20"/>
-      <c r="BP51" s="20"/>
-      <c r="BQ51" s="20"/>
-      <c r="BR51" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20668,131 +20090,115 @@
     <hyperlink ref="M36" r:id="rId273" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N36" r:id="rId274"/>
     <hyperlink ref="AW36" r:id="rId275" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2C07IHD2U23I5"/>
-    <hyperlink ref="C37" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B0H8SPVHVZ"/>
-    <hyperlink ref="G37" r:id="rId277" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%81%8D%E3%82%8C%E3%81%84%E3%81%AE%E6%99%82%E9%96%93%E3%82%92%E3%80%81%E7%A7%81%E3%81%AE%E6%99%82%E9%96%93%E3%81%AB%E3%80%82/page/B441CACF-20A2-4071-9530-2CC8DA3A24B6?lp_asin=B0H8SPVHVZ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J37" r:id="rId278" tooltip="https://www.amazon.co.jp/dp/B0H8SPVHVZ?psc=1"/>
-    <hyperlink ref="K37" r:id="rId279" tooltip="https://m.media-amazon.com/images/I/418sjd-uV7L._AC_US600_.jpg"/>
-    <hyperlink ref="L37" r:id="rId280" tooltip="https://www.amazon.co.jp/dp/B0GLQ3BZZT"/>
+    <hyperlink ref="C37" r:id="rId276" tooltip="https://www.amazon.co.jp/dp/B005MWZKNI"/>
+    <hyperlink ref="G37" r:id="rId277" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B005MWZKNI&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J37" r:id="rId278" tooltip="https://www.amazon.co.jp/dp/B005MWZKNI?psc=1"/>
+    <hyperlink ref="K37" r:id="rId279" tooltip="https://m.media-amazon.com/images/I/41ag3BndzyL._AC_US600_.jpg"/>
+    <hyperlink ref="L37" r:id="rId280" tooltip="https://www.amazon.co.jp/dp/B005MWZKNI"/>
     <hyperlink ref="M37" r:id="rId281" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N37" r:id="rId282"/>
-    <hyperlink ref="AW37" r:id="rId283" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3WKMH8N8T04I"/>
-    <hyperlink ref="C38" r:id="rId284" tooltip="https://www.amazon.co.jp/dp/B005MWZKNI"/>
-    <hyperlink ref="G38" r:id="rId285" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B005MWZKNI&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J38" r:id="rId286" tooltip="https://www.amazon.co.jp/dp/B005MWZKNI?psc=1"/>
-    <hyperlink ref="K38" r:id="rId287" tooltip="https://m.media-amazon.com/images/I/41ag3BndzyL._AC_US600_.jpg"/>
-    <hyperlink ref="L38" r:id="rId288" tooltip="https://www.amazon.co.jp/dp/B005MWZKNI"/>
+    <hyperlink ref="AW37" r:id="rId283" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=APF7PXDXK20CB"/>
+    <hyperlink ref="C38" r:id="rId284" tooltip="https://www.amazon.co.jp/dp/B0H74P4ZMB"/>
+    <hyperlink ref="G38" r:id="rId285" tooltip="https://www.amazon.co.jp/-/zh/stores/Yadea/page/DE8B12B7-0E18-4304-A0FC-F26833052784?lp_asin=B0H74P4ZMB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J38" r:id="rId286" tooltip="https://www.amazon.co.jp/dp/B0H74P4ZMB?psc=1"/>
+    <hyperlink ref="K38" r:id="rId287" tooltip="https://images-na.ssl-images-amazon.com/images/I/71INq-jTsbL._AC_US600_.jpg"/>
+    <hyperlink ref="L38" r:id="rId288" tooltip="https://www.amazon.co.jp/dp/B0HHHTZ3LQ"/>
     <hyperlink ref="M38" r:id="rId289" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N38" r:id="rId290"/>
-    <hyperlink ref="AW38" r:id="rId291" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=APF7PXDXK20CB"/>
-    <hyperlink ref="C39" r:id="rId292" tooltip="https://www.amazon.co.jp/dp/B0H74P4ZMB"/>
-    <hyperlink ref="G39" r:id="rId293" tooltip="https://www.amazon.co.jp/-/zh/stores/Yadea/page/DE8B12B7-0E18-4304-A0FC-F26833052784?lp_asin=B0H74P4ZMB&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J39" r:id="rId294" tooltip="https://www.amazon.co.jp/dp/B0H74P4ZMB?psc=1"/>
-    <hyperlink ref="K39" r:id="rId295" tooltip="https://images-na.ssl-images-amazon.com/images/I/71INq-jTsbL._AC_US600_.jpg"/>
-    <hyperlink ref="L39" r:id="rId296" tooltip="https://www.amazon.co.jp/dp/B0HHHTZ3LQ"/>
+    <hyperlink ref="AW38" r:id="rId291" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FFZRDLOQM7BY"/>
+    <hyperlink ref="C39" r:id="rId292" tooltip="https://www.amazon.co.jp/dp/B0BL6RYNQ2"/>
+    <hyperlink ref="G39" r:id="rId293" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0BL6RYNQ2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J39" r:id="rId294" tooltip="https://www.amazon.co.jp/dp/B0BL6RYNQ2?psc=1"/>
+    <hyperlink ref="K39" r:id="rId295" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31i885y+FLL._AC_US600_.jpg"/>
+    <hyperlink ref="L39" r:id="rId296" tooltip="https://www.amazon.co.jp/dp/B0BL6RYNQ2"/>
     <hyperlink ref="M39" r:id="rId297" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N39" r:id="rId298"/>
-    <hyperlink ref="AW39" r:id="rId299" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1FFZRDLOQM7BY"/>
-    <hyperlink ref="C40" r:id="rId300" tooltip="https://www.amazon.co.jp/dp/B0BL6RYNQ2"/>
-    <hyperlink ref="G40" r:id="rId301" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%82%A2%E3%82%A4%E3%83%AA%E3%82%B9%E3%82%AA%E3%83%BC%E3%83%A4%E3%83%9E/page/1DA544F1-992D-41FB-B28D-3CD2657D962F?lp_asin=B0BL6RYNQ2&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J40" r:id="rId302" tooltip="https://www.amazon.co.jp/dp/B0BL6RYNQ2?psc=1"/>
-    <hyperlink ref="K40" r:id="rId303" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31i885y+FLL._AC_US600_.jpg"/>
-    <hyperlink ref="L40" r:id="rId304" tooltip="https://www.amazon.co.jp/dp/B0BL6RYNQ2"/>
+    <hyperlink ref="AW39" r:id="rId299" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2GDOHXNU39HXM"/>
+    <hyperlink ref="C40" r:id="rId300" tooltip="https://www.amazon.co.jp/dp/B0H89ZR9LV"/>
+    <hyperlink ref="G40" r:id="rId301" tooltip="https://www.amazon.co.jp/-/zh/GOBOT/b/ref=bl_dp_s_web_7090029051?ie=UTF8&amp;node=7090029051&amp;field-lbr_brands_browse-bin=GOBOT"/>
+    <hyperlink ref="J40" r:id="rId302" tooltip="https://www.amazon.co.jp/dp/B0H89ZR9LV?psc=1"/>
+    <hyperlink ref="K40" r:id="rId303" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31sEmiQ15AL._AC_US600_.jpg"/>
+    <hyperlink ref="L40" r:id="rId304" tooltip="https://www.amazon.co.jp/dp/B0H89ZR9LV"/>
     <hyperlink ref="M40" r:id="rId305" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N40" r:id="rId306"/>
-    <hyperlink ref="AW40" r:id="rId307" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2GDOHXNU39HXM"/>
-    <hyperlink ref="C41" r:id="rId308" tooltip="https://www.amazon.co.jp/dp/B0H89ZR9LV"/>
-    <hyperlink ref="G41" r:id="rId309" tooltip="https://www.amazon.co.jp/-/zh/GOBOT/b/ref=bl_dp_s_web_7090029051?ie=UTF8&amp;node=7090029051&amp;field-lbr_brands_browse-bin=GOBOT"/>
-    <hyperlink ref="J41" r:id="rId310" tooltip="https://www.amazon.co.jp/dp/B0H89ZR9LV?psc=1"/>
-    <hyperlink ref="K41" r:id="rId311" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/31sEmiQ15AL._AC_US600_.jpg"/>
-    <hyperlink ref="L41" r:id="rId312" tooltip="https://www.amazon.co.jp/dp/B0H89ZR9LV"/>
+    <hyperlink ref="AW40" r:id="rId307" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KZHF5181BFVZ"/>
+    <hyperlink ref="C41" r:id="rId308" tooltip="https://www.amazon.co.jp/dp/B0GF8HHWYQ"/>
+    <hyperlink ref="G41" r:id="rId309" tooltip="https://www.amazon.co.jp/-/zh/stores/Mistsince/page/D3BF9035-65AB-4860-9B3C-F101376ACA73?lp_asin=B0GF8HHWYQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J41" r:id="rId310" tooltip="https://www.amazon.co.jp/dp/B0GF8HHWYQ?psc=1"/>
+    <hyperlink ref="K41" r:id="rId311" tooltip="https://m.media-amazon.com/images/I/41z5edZXbeL._AC_US600_.jpg"/>
+    <hyperlink ref="L41" r:id="rId312" tooltip="https://www.amazon.co.jp/dp/B0GXYJC1JK"/>
     <hyperlink ref="M41" r:id="rId313" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N41" r:id="rId314"/>
-    <hyperlink ref="AW41" r:id="rId315" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2KZHF5181BFVZ"/>
-    <hyperlink ref="C42" r:id="rId316" tooltip="https://www.amazon.co.jp/dp/B0GF8HHWYQ"/>
-    <hyperlink ref="G42" r:id="rId317" tooltip="https://www.amazon.co.jp/-/zh/stores/Mistsince/page/D3BF9035-65AB-4860-9B3C-F101376ACA73?lp_asin=B0GF8HHWYQ&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J42" r:id="rId318" tooltip="https://www.amazon.co.jp/dp/B0GF8HHWYQ?psc=1"/>
-    <hyperlink ref="K42" r:id="rId319" tooltip="https://m.media-amazon.com/images/I/41z5edZXbeL._AC_US600_.jpg"/>
-    <hyperlink ref="L42" r:id="rId320" tooltip="https://www.amazon.co.jp/dp/B0GXYJC1JK"/>
+    <hyperlink ref="AW41" r:id="rId315" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AVZ7LMXDP1WK4"/>
+    <hyperlink ref="C42" r:id="rId316" tooltip="https://www.amazon.co.jp/dp/B0B3XBM5HW"/>
+    <hyperlink ref="G42" r:id="rId317" tooltip="https://www.amazon.co.jp/stores/%E3%82%B1%E3%83%AB%E3%83%92%E3%83%A3%E3%83%BCKARCHER/page/C3335239-5EF7-43A7-B432-CEBBBE4E3C9B?lp_asin=B0B3XBM5HW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J42" r:id="rId318" tooltip="https://www.amazon.co.jp/dp/B0B3XBM5HW?psc=1"/>
+    <hyperlink ref="K42" r:id="rId319" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/51Sf-O7BUfL._AC_US600_.jpg"/>
+    <hyperlink ref="L42" r:id="rId320" tooltip="https://www.amazon.co.jp/dp/B0B3XBM5HW"/>
     <hyperlink ref="M42" r:id="rId321" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N42" r:id="rId322"/>
-    <hyperlink ref="AW42" r:id="rId323" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AVZ7LMXDP1WK4"/>
-    <hyperlink ref="C43" r:id="rId324" tooltip="https://www.amazon.co.jp/dp/B0B3XBM5HW"/>
-    <hyperlink ref="G43" r:id="rId325" tooltip="https://www.amazon.co.jp/stores/%E3%82%B1%E3%83%AB%E3%83%92%E3%83%A3%E3%83%BCKARCHER/page/C3335239-5EF7-43A7-B432-CEBBBE4E3C9B?lp_asin=B0B3XBM5HW&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J43" r:id="rId326" tooltip="https://www.amazon.co.jp/dp/B0B3XBM5HW?psc=1"/>
-    <hyperlink ref="K43" r:id="rId327" tooltip="https://m.media-amazon.com/images/W/BW_MEDIAX_AVIF_MEASUREMENT_1306696-T2/images/I/51Sf-O7BUfL._AC_US600_.jpg"/>
-    <hyperlink ref="L43" r:id="rId328" tooltip="https://www.amazon.co.jp/dp/B0B3XBM5HW"/>
+    <hyperlink ref="AW42" r:id="rId323" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EFLM9LIB8P2E"/>
+    <hyperlink ref="C43" r:id="rId324" tooltip="https://www.amazon.co.jp/dp/B0HBNN64GG"/>
+    <hyperlink ref="G43" r:id="rId325" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=PROSTREET"/>
+    <hyperlink ref="J43" r:id="rId326" tooltip="https://www.amazon.co.jp/dp/B0HBNN64GG?psc=1"/>
+    <hyperlink ref="K43" r:id="rId327" tooltip="https://images-na.ssl-images-amazon.com/images/I/61SWPhDh01L._AC_US600_.jpg"/>
+    <hyperlink ref="L43" r:id="rId328" tooltip="https://www.amazon.co.jp/dp/B0HBNN64GG"/>
     <hyperlink ref="M43" r:id="rId329" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N43" r:id="rId330"/>
-    <hyperlink ref="AW43" r:id="rId331" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A3EFLM9LIB8P2E"/>
-    <hyperlink ref="C44" r:id="rId332" tooltip="https://www.amazon.co.jp/dp/B0HBNN64GG"/>
-    <hyperlink ref="G44" r:id="rId333" tooltip="https://www.amazon.co.jp/-/zh/s/ref=bl_dp_s_web_0?ie=UTF8&amp;search-type=ss&amp;index=kitchen-jp&amp;field-keywords=PROSTREET"/>
-    <hyperlink ref="J44" r:id="rId334" tooltip="https://www.amazon.co.jp/dp/B0HBNN64GG?psc=1"/>
-    <hyperlink ref="K44" r:id="rId335" tooltip="https://images-na.ssl-images-amazon.com/images/I/61SWPhDh01L._AC_US600_.jpg"/>
-    <hyperlink ref="L44" r:id="rId336" tooltip="https://www.amazon.co.jp/dp/B0HBNN64GG"/>
+    <hyperlink ref="AW43" r:id="rId331" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YO7910ANGPIW"/>
+    <hyperlink ref="C44" r:id="rId332" tooltip="https://www.amazon.co.jp/dp/B0DRCGRJSR"/>
+    <hyperlink ref="G44" r:id="rId333" tooltip="https://www.amazon.co.jp/-/zh/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0DRCGRJSR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
+    <hyperlink ref="J44" r:id="rId334" tooltip="https://www.amazon.co.jp/dp/B0DRCGRJSR?psc=1"/>
+    <hyperlink ref="K44" r:id="rId335" tooltip="https://m.media-amazon.com/images/I/41wLqF+bzbL._AC_US600_.jpg"/>
+    <hyperlink ref="L44" r:id="rId336" tooltip="https://www.amazon.co.jp/dp/B0F486YKK4"/>
     <hyperlink ref="M44" r:id="rId337" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N44" r:id="rId338"/>
-    <hyperlink ref="AW44" r:id="rId339" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A2YO7910ANGPIW"/>
-    <hyperlink ref="C45" r:id="rId340" tooltip="https://www.amazon.co.jp/dp/B08R3LF57P"/>
-    <hyperlink ref="G45" r:id="rId341" tooltip="https://www.amazon.co.jp/-/zh/stores/KEEPOW/page/21523984-F72B-4ED5-8C28-45B0588E2513?lp_asin=B08R3LF57P&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J45" r:id="rId342" tooltip="https://www.amazon.co.jp/dp/B08R3LF57P?psc=1"/>
-    <hyperlink ref="K45" r:id="rId343" tooltip="https://images-na.ssl-images-amazon.com/images/I/41AHQ4cHR8L._AC_US600_.jpg"/>
-    <hyperlink ref="L45" r:id="rId344" tooltip="https://www.amazon.co.jp/dp/B0DBHX5TKK"/>
+    <hyperlink ref="AW44" r:id="rId339" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES"/>
+    <hyperlink ref="C45" r:id="rId340" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN"/>
+    <hyperlink ref="G45" r:id="rId341" tooltip="https://www.amazon.co.jp/-/zh/stores/Waitbird/page/3EF06D38-11FF-4AB3-B913-B77B78E9E2C6?lp_asin=B0HK3489BN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
+    <hyperlink ref="J45" r:id="rId342" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN?psc=1"/>
+    <hyperlink ref="K45" r:id="rId343" tooltip="https://m.media-amazon.com/images/I/41uxuzLFDeL._AC_US600_.jpg"/>
+    <hyperlink ref="L45" r:id="rId344" tooltip="https://www.amazon.co.jp/dp/B0HKMPN41V"/>
     <hyperlink ref="M45" r:id="rId345" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N45" r:id="rId346"/>
-    <hyperlink ref="AW45" r:id="rId347" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A30T80D6SCTMYZ"/>
-    <hyperlink ref="C46" r:id="rId348" tooltip="https://www.amazon.co.jp/dp/B0DRCGRJSR"/>
-    <hyperlink ref="G46" r:id="rId349" tooltip="https://www.amazon.co.jp/-/zh/stores/HAUSHOF/page/AE1183BD-5A16-470E-862E-30886B891342?lp_asin=B0DRCGRJSR&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto&amp;bl_grd_status=override"/>
-    <hyperlink ref="J46" r:id="rId350" tooltip="https://www.amazon.co.jp/dp/B0DRCGRJSR?psc=1"/>
-    <hyperlink ref="K46" r:id="rId351" tooltip="https://m.media-amazon.com/images/I/41wLqF+bzbL._AC_US600_.jpg"/>
-    <hyperlink ref="L46" r:id="rId352" tooltip="https://www.amazon.co.jp/dp/B0F486YKK4"/>
+    <hyperlink ref="AW45" r:id="rId347" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSFAH2380FVF"/>
+    <hyperlink ref="C46" r:id="rId348" tooltip="https://www.amazon.co.jp/dp/B01BEH1OAC"/>
+    <hyperlink ref="G46" r:id="rId349" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%83%80%E3%82%A4%E3%83%AC%E3%82%AF%E3%83%88%E3%83%86%E3%83%AC%E3%82%B7%E3%83%A7%E3%83%83%E3%83%97/page/5C9F3767-423D-4E02-98FC-726D8B2F56AE?lp_asin=B01BEH1OAC&amp;ref_=ast_bln"/>
+    <hyperlink ref="J46" r:id="rId350" tooltip="https://www.amazon.co.jp/dp/B01BEH1OAC?psc=1"/>
+    <hyperlink ref="K46" r:id="rId351" tooltip="https://m.media-amazon.com/images/I/51cWEc-X2YL._AC_US600_.jpg"/>
+    <hyperlink ref="L46" r:id="rId352" tooltip="https://www.amazon.co.jp/dp/B0151FQ7MI"/>
     <hyperlink ref="M46" r:id="rId353" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N46" r:id="rId354"/>
-    <hyperlink ref="AW46" r:id="rId355" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=ADXIWAI1CZVES"/>
-    <hyperlink ref="C47" r:id="rId356" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN"/>
-    <hyperlink ref="G47" r:id="rId357" tooltip="https://www.amazon.co.jp/-/zh/stores/Waitbird/page/3EF06D38-11FF-4AB3-B913-B77B78E9E2C6?lp_asin=B0HK3489BN&amp;ref_=ast_bln&amp;store_ref=bl_ast_dp_brandlogo_sto"/>
-    <hyperlink ref="J47" r:id="rId358" tooltip="https://www.amazon.co.jp/dp/B0HK3489BN?psc=1"/>
-    <hyperlink ref="K47" r:id="rId359" tooltip="https://m.media-amazon.com/images/I/41uxuzLFDeL._AC_US600_.jpg"/>
-    <hyperlink ref="L47" r:id="rId360" tooltip="https://www.amazon.co.jp/dp/B0HKMPN41V"/>
+    <hyperlink ref="AW46" r:id="rId355" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JVN30QXJB2BN"/>
+    <hyperlink ref="C47" r:id="rId356" tooltip="https://www.amazon.co.jp/dp/B07GXPG63H"/>
+    <hyperlink ref="G47" r:id="rId357" tooltip="https://www.amazon.co.jpnull"/>
+    <hyperlink ref="J47" r:id="rId358" tooltip="https://www.amazon.co.jp/dp/B07GXPG63H?psc=1"/>
+    <hyperlink ref="K47" r:id="rId359" tooltip="https://m.media-amazon.com/images/I/41H+7reLbSL._AC_US200_.jpg"/>
+    <hyperlink ref="L47" r:id="rId360" tooltip="https://www.amazon.co.jp/dp/B07GXPG63H"/>
     <hyperlink ref="M47" r:id="rId361" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
     <hyperlink ref="N47" r:id="rId362"/>
-    <hyperlink ref="AW47" r:id="rId363" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=AYSFAH2380FVF"/>
-    <hyperlink ref="C48" r:id="rId364" tooltip="https://www.amazon.co.jp/dp/B01BEH1OAC"/>
-    <hyperlink ref="G48" r:id="rId365" tooltip="https://www.amazon.co.jp/-/zh/stores/%E3%83%80%E3%82%A4%E3%83%AC%E3%82%AF%E3%83%88%E3%83%86%E3%83%AC%E3%82%B7%E3%83%A7%E3%83%83%E3%83%97/page/5C9F3767-423D-4E02-98FC-726D8B2F56AE?lp_asin=B01BEH1OAC&amp;ref_=ast_bln"/>
-    <hyperlink ref="J48" r:id="rId366" tooltip="https://www.amazon.co.jp/dp/B01BEH1OAC?psc=1"/>
-    <hyperlink ref="K48" r:id="rId367" tooltip="https://m.media-amazon.com/images/I/51cWEc-X2YL._AC_US600_.jpg"/>
-    <hyperlink ref="L48" r:id="rId368" tooltip="https://www.amazon.co.jp/dp/B0151FQ7MI"/>
-    <hyperlink ref="M48" r:id="rId369" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
-    <hyperlink ref="N48" r:id="rId370"/>
-    <hyperlink ref="AW48" r:id="rId371" tooltip="https://www.amazon.co.jp/gp/help/seller/at-a-glance.html/ref=dp_merchant_link?seller=A1JVN30QXJB2BN"/>
-    <hyperlink ref="C49" r:id="rId372" tooltip="https://www.amazon.co.jp/dp/B07GXPG63H"/>
-    <hyperlink ref="G49" r:id="rId373" tooltip="https://www.amazon.co.jpnull"/>
-    <hyperlink ref="J49" r:id="rId374" tooltip="https://www.amazon.co.jp/dp/B07GXPG63H?psc=1"/>
-    <hyperlink ref="K49" r:id="rId375" tooltip="https://m.media-amazon.com/images/I/41H+7reLbSL._AC_US200_.jpg"/>
-    <hyperlink ref="L49" r:id="rId376" tooltip="https://www.amazon.co.jp/dp/B07GXPG63H"/>
-    <hyperlink ref="M49" r:id="rId377" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
-    <hyperlink ref="N49" r:id="rId378"/>
-    <hyperlink ref="C50" r:id="rId379" tooltip="https://www.amazon.co.jp/dp/B0CZ3YBX8C"/>
-    <hyperlink ref="G50" r:id="rId380" tooltip="https://www.amazon.co.jpnull"/>
-    <hyperlink ref="J50" r:id="rId381" tooltip="https://www.amazon.co.jp/dp/B0CZ3YBX8C?psc=1"/>
-    <hyperlink ref="K50" r:id="rId382" tooltip="https://m.media-amazon.com/images/I/31nhFm22HvL._AC_US200_.jpg"/>
-    <hyperlink ref="L50" r:id="rId383" tooltip="https://www.amazon.co.jp/dp/B0F5W9SGVC"/>
-    <hyperlink ref="M50" r:id="rId384" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
-    <hyperlink ref="N50" r:id="rId385"/>
-    <hyperlink ref="C51" r:id="rId386" tooltip="https://www.amazon.co.jp/dp/B0HKBW4BLR"/>
-    <hyperlink ref="G51" r:id="rId387" tooltip="https://www.amazon.co.jp/-/zh/Bissell/b/ref=bl_dp_s_web_220431009051?ie=UTF8&amp;node=220431009051&amp;field-lbr_brands_browse-bin=Bissell"/>
-    <hyperlink ref="J51" r:id="rId388" tooltip="https://www.amazon.co.jp/dp/B0HKBW4BLR?psc=1"/>
-    <hyperlink ref="K51" r:id="rId389" tooltip="https://m.media-amazon.com/images/I/41Pe+u97axL._AC_US200_.jpg"/>
-    <hyperlink ref="L51" r:id="rId390" tooltip="https://www.amazon.co.jp/dp/B0HKD7LVQY"/>
-    <hyperlink ref="M51" r:id="rId391" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
-    <hyperlink ref="N51" r:id="rId392"/>
+    <hyperlink ref="C48" r:id="rId363" tooltip="https://www.amazon.co.jp/dp/B0CZ3YBX8C"/>
+    <hyperlink ref="G48" r:id="rId364" tooltip="https://www.amazon.co.jpnull"/>
+    <hyperlink ref="J48" r:id="rId365" tooltip="https://www.amazon.co.jp/dp/B0CZ3YBX8C?psc=1"/>
+    <hyperlink ref="K48" r:id="rId366" tooltip="https://m.media-amazon.com/images/I/31nhFm22HvL._AC_US200_.jpg"/>
+    <hyperlink ref="L48" r:id="rId367" tooltip="https://www.amazon.co.jp/dp/B0F5W9SGVC"/>
+    <hyperlink ref="M48" r:id="rId368" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
+    <hyperlink ref="N48" r:id="rId369"/>
+    <hyperlink ref="C49" r:id="rId370" tooltip="https://www.amazon.co.jp/dp/B0HKBW4BLR"/>
+    <hyperlink ref="G49" r:id="rId371" tooltip="https://www.amazon.co.jp/-/zh/Bissell/b/ref=bl_dp_s_web_220431009051?ie=UTF8&amp;node=220431009051&amp;field-lbr_brands_browse-bin=Bissell"/>
+    <hyperlink ref="J49" r:id="rId372" tooltip="https://www.amazon.co.jp/dp/B0HKBW4BLR?psc=1"/>
+    <hyperlink ref="K49" r:id="rId373" tooltip="https://m.media-amazon.com/images/I/41Pe+u97axL._AC_US200_.jpg"/>
+    <hyperlink ref="L49" r:id="rId374" tooltip="https://www.amazon.co.jp/dp/B0HKD7LVQY"/>
+    <hyperlink ref="M49" r:id="rId375" tooltip="https://www.amazon.co.jp/b?node=2466960051"/>
+    <hyperlink ref="N49" r:id="rId376"/>
   </hyperlinks>
-  <drawing r:id="rId393"/>
+  <drawing r:id="rId377"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G29"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -20856,7 +20262,7 @@
         <v>13811.007347352419</v>
       </c>
       <c r="G2" s="19">
-        <v>0.35619528923382365</v>
+        <v>0.35983225453550916</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20877,7 +20283,7 @@
         <v>32931.975155279506</v>
       </c>
       <c r="G3" s="19">
-        <v>0.08717624763108023</v>
+        <v>0.08806636885768986</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20898,7 +20304,7 @@
         <v>12085.5487752471</v>
       </c>
       <c r="G4" s="19">
-        <v>0.20999909755437235</v>
+        <v>0.2121433129729237</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20919,7 +20325,7 @@
         <v>19020.971393034826</v>
       </c>
       <c r="G5" s="19">
-        <v>0.0725566284631351</v>
+        <v>0.0732974747014313</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20940,7 +20346,7 @@
         <v>28800.0</v>
       </c>
       <c r="G6" s="19">
-        <v>0.021839184189152604</v>
+        <v>0.022062175221077583</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20961,7 +20367,7 @@
         <v>28419.0</v>
       </c>
       <c r="G7" s="19">
-        <v>0.013446439851998917</v>
+        <v>0.013583735983225454</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -20982,7 +20388,7 @@
         <v>15980.0</v>
       </c>
       <c r="G8" s="19">
-        <v>0.021839184189152604</v>
+        <v>0.022062175221077583</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21003,7 +20409,7 @@
         <v>29800.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.011280570345636676</v>
+        <v>0.011395751663779742</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21024,7 +20430,7 @@
         <v>21428.06976744186</v>
       </c>
       <c r="G10" s="19">
-        <v>0.015522064795596065</v>
+        <v>0.015680554289360927</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21045,70 +20451,70 @@
         <v>14990.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.02066600487320639</v>
+        <v>0.02087701704804449</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>evove</t>
+          <t>M Mistsince</t>
         </is>
       </c>
       <c r="B12" s="13">
-        <v>338</v>
+        <v>291</v>
       </c>
       <c r="C12" s="13">
-        <v>2835062</v>
+        <v>2507093</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13">
-        <v>8387.757396449704</v>
+        <v>8615.439862542955</v>
       </c>
       <c r="G12" s="19">
-        <v>0.03050266221460157</v>
+        <v>0.02652930987327924</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>M Mistsince</t>
+          <t>Shark</t>
         </is>
       </c>
       <c r="B13" s="13">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="C13" s="13">
-        <v>2507093</v>
+        <v>2276109</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13">
-        <v>8615.439862542955</v>
+        <v>8217.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.02626116776464218</v>
+        <v>0.02525298568693591</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>Shark</t>
+          <t>evove</t>
         </is>
       </c>
       <c r="B14" s="13">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C14" s="13">
-        <v>2276109</v>
+        <v>2275132</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13">
-        <v>8217.0</v>
+        <v>8489.298507462687</v>
       </c>
       <c r="G14" s="19">
-        <v>0.024997743885930873</v>
+        <v>0.02443249156714377</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21129,7 +20535,7 @@
         <v>13997.5</v>
       </c>
       <c r="G15" s="19">
-        <v>0.014439130042414944</v>
+        <v>0.01458656212963807</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21150,7 +20556,7 @@
         <v>10383.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.0177781788647234</v>
+        <v>0.017959704622116875</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21171,7 +20577,7 @@
         <v>13980.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.011461059471166862</v>
+        <v>0.011578083690400219</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21192,7 +20598,7 @@
         <v>19900.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.006678097644616912</v>
+        <v>0.006746284984957608</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21213,7 +20619,7 @@
         <v>15293.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.006858586770147099</v>
+        <v>0.006928617011578084</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21234,7 +20640,7 @@
         <v>14508.0</v>
       </c>
       <c r="G20" s="19">
-        <v>0.005504918328670698</v>
+        <v>0.005561126811924514</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21255,7 +20661,7 @@
         <v>19935.0</v>
       </c>
       <c r="G21" s="19">
-        <v>0.00397076076166411</v>
+        <v>0.004011304585650469</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21276,7 +20682,7 @@
         <v>23800.0</v>
       </c>
       <c r="G22" s="19">
-        <v>0.002887826008482989</v>
+        <v>0.0029173124259276144</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21297,7 +20703,7 @@
         <v>9980.0</v>
       </c>
       <c r="G23" s="19">
-        <v>0.006768342207382005</v>
+        <v>0.006837450998267846</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21318,7 +20724,7 @@
         <v>11850.0</v>
       </c>
       <c r="G24" s="19">
-        <v>0.0029780705712480825</v>
+        <v>0.003008478439237852</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21339,109 +20745,88 @@
         <v>14000.0</v>
       </c>
       <c r="G25" s="19">
-        <v>0.000902445627650934</v>
+        <v>0.0009116601331023794</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>KEEPOW</t>
+          <t>HAUSHOF</t>
         </is>
       </c>
       <c r="B26" s="13">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C26" s="13">
-        <v>96558</v>
+        <v>95680</v>
       </c>
       <c r="D26" s="13"/>
       <c r="E26" s="13"/>
       <c r="F26" s="13">
-        <v>2299.0</v>
+        <v>5980.0</v>
       </c>
       <c r="G26" s="19">
-        <v>0.003790271636133923</v>
+        <v>0.0014586562129638072</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>HAUSHOF</t>
+          <t>Waitbird</t>
         </is>
       </c>
       <c r="B27" s="13">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C27" s="13">
-        <v>95680</v>
+        <v>75952</v>
       </c>
       <c r="D27" s="13"/>
       <c r="E27" s="13"/>
       <c r="F27" s="13">
-        <v>5980.0</v>
+        <v>9494.0</v>
       </c>
       <c r="G27" s="19">
-        <v>0.0014439130042414945</v>
+        <v>0.0007293281064819036</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Waitbird</t>
+          <t>H2O STEAMFX</t>
         </is>
       </c>
       <c r="B28" s="13">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C28" s="13">
-        <v>75952</v>
+        <v>74188</v>
       </c>
       <c r="D28" s="13"/>
       <c r="E28" s="13"/>
       <c r="F28" s="13">
-        <v>9494.0</v>
+        <v>4364.0</v>
       </c>
       <c r="G28" s="19">
-        <v>0.0007219565021207473</v>
+        <v>0.001549822226274045</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>H2O STEAMFX</t>
+          <t>Bissell</t>
         </is>
       </c>
       <c r="B29" s="13">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C29" s="13">
-        <v>74188</v>
+        <v>0</v>
       </c>
       <c r="D29" s="13"/>
       <c r="E29" s="13"/>
-      <c r="F29" s="13">
-        <v>4364.0</v>
-      </c>
+      <c r="F29" s="13"/>
       <c r="G29" s="19">
-        <v>0.001534157567006588</v>
-      </c>
-    </row>
-    <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="12" t="inlineStr">
-        <is>
-          <t>Bissell</t>
-        </is>
-      </c>
-      <c r="B30" s="13">
-        <v>0</v>
-      </c>
-      <c r="C30" s="13">
-        <v>0</v>
-      </c>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
-      <c r="G30" s="19">
         <v>0.0</v>
       </c>
     </row>
@@ -21453,7 +20838,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G35"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="25" style="1" customWidth="1"/>
@@ -21517,7 +20902,7 @@
         <v>18652.144912985274</v>
       </c>
       <c r="G2" s="19">
-        <v>0.2696507535420991</v>
+        <v>0.272404047770991</v>
       </c>
     </row>
     <row r="3" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21538,7 +20923,7 @@
         <v>13811.007347352419</v>
       </c>
       <c r="G3" s="19">
-        <v>0.35619528923382365</v>
+        <v>0.35983225453550916</v>
       </c>
     </row>
     <row r="4" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21559,7 +20944,7 @@
         <v>19020.971393034826</v>
       </c>
       <c r="G4" s="19">
-        <v>0.0725566284631351</v>
+        <v>0.0732974747014313</v>
       </c>
     </row>
     <row r="5" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21580,7 +20965,7 @@
         <v>28800.0</v>
       </c>
       <c r="G5" s="19">
-        <v>0.021839184189152604</v>
+        <v>0.022062175221077583</v>
       </c>
     </row>
     <row r="6" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21601,7 +20986,7 @@
         <v>28419.0</v>
       </c>
       <c r="G6" s="19">
-        <v>0.013446439851998917</v>
+        <v>0.013583735983225454</v>
       </c>
     </row>
     <row r="7" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21622,7 +21007,7 @@
         <v>15980.0</v>
       </c>
       <c r="G7" s="19">
-        <v>0.021839184189152604</v>
+        <v>0.022062175221077583</v>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21643,7 +21028,7 @@
         <v>29800.0</v>
       </c>
       <c r="G8" s="19">
-        <v>0.011280570345636676</v>
+        <v>0.011395751663779742</v>
       </c>
     </row>
     <row r="9" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21664,7 +21049,7 @@
         <v>14990.0</v>
       </c>
       <c r="G9" s="19">
-        <v>0.02066600487320639</v>
+        <v>0.02087701704804449</v>
       </c>
     </row>
     <row r="10" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21685,91 +21070,91 @@
         <v>11700.0</v>
       </c>
       <c r="G10" s="19">
-        <v>0.022380651565743166</v>
+        <v>0.02260917130093901</v>
       </c>
     </row>
     <row r="11" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="12" t="inlineStr">
         <is>
-          <t>EVOVE</t>
+          <t>GKK公式直営・安心保証</t>
         </is>
       </c>
       <c r="B11" s="13">
-        <v>338</v>
+        <v>123</v>
       </c>
       <c r="C11" s="13">
-        <v>2835062</v>
+        <v>2656677</v>
       </c>
       <c r="D11" s="13"/>
       <c r="E11" s="13"/>
       <c r="F11" s="13">
-        <v>8387.757396449704</v>
+        <v>21599.0</v>
       </c>
       <c r="G11" s="19">
-        <v>0.03050266221460157</v>
+        <v>0.011213419637159267</v>
       </c>
     </row>
     <row r="12" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="12" t="inlineStr">
         <is>
-          <t>GKK公式直営・安心保証</t>
+          <t>Mistsince</t>
         </is>
       </c>
       <c r="B12" s="13">
-        <v>123</v>
+        <v>291</v>
       </c>
       <c r="C12" s="13">
-        <v>2656677</v>
+        <v>2507093</v>
       </c>
       <c r="D12" s="13"/>
       <c r="E12" s="13"/>
       <c r="F12" s="13">
-        <v>21599.0</v>
+        <v>8615.439862542955</v>
       </c>
       <c r="G12" s="19">
-        <v>0.011100081220106488</v>
+        <v>0.02652930987327924</v>
       </c>
     </row>
     <row r="13" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A13" s="12" t="inlineStr">
         <is>
-          <t>Mistsince</t>
+          <t>D shopone</t>
         </is>
       </c>
       <c r="B13" s="13">
-        <v>291</v>
+        <v>277</v>
       </c>
       <c r="C13" s="13">
-        <v>2507093</v>
+        <v>2276109</v>
       </c>
       <c r="D13" s="13"/>
       <c r="E13" s="13"/>
       <c r="F13" s="13">
-        <v>8615.439862542955</v>
+        <v>8217.0</v>
       </c>
       <c r="G13" s="19">
-        <v>0.02626116776464218</v>
+        <v>0.02525298568693591</v>
       </c>
     </row>
     <row r="14" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A14" s="12" t="inlineStr">
         <is>
-          <t>D shopone</t>
+          <t>EVOVE</t>
         </is>
       </c>
       <c r="B14" s="13">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="C14" s="13">
-        <v>2276109</v>
+        <v>2275132</v>
       </c>
       <c r="D14" s="13"/>
       <c r="E14" s="13"/>
       <c r="F14" s="13">
-        <v>8217.0</v>
+        <v>8489.298507462687</v>
       </c>
       <c r="G14" s="19">
-        <v>0.024997743885930873</v>
+        <v>0.02443249156714377</v>
       </c>
     </row>
     <row r="15" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21790,7 +21175,7 @@
         <v>13997.5</v>
       </c>
       <c r="G15" s="19">
-        <v>0.014439130042414944</v>
+        <v>0.01458656212963807</v>
       </c>
     </row>
     <row r="16" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21811,7 +21196,7 @@
         <v>13980.0</v>
       </c>
       <c r="G16" s="19">
-        <v>0.011461059471166862</v>
+        <v>0.011578083690400219</v>
       </c>
     </row>
     <row r="17" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21832,7 +21217,7 @@
         <v>19900.0</v>
       </c>
       <c r="G17" s="19">
-        <v>0.006678097644616912</v>
+        <v>0.006746284984957608</v>
       </c>
     </row>
     <row r="18" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21853,7 +21238,7 @@
         <v>15293.0</v>
       </c>
       <c r="G18" s="19">
-        <v>0.006858586770147099</v>
+        <v>0.006928617011578084</v>
       </c>
     </row>
     <row r="19" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21874,7 +21259,7 @@
         <v>18062.0</v>
       </c>
       <c r="G19" s="19">
-        <v>0.005414673765905605</v>
+        <v>0.0054699607986142765</v>
       </c>
     </row>
     <row r="20" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21895,7 +21280,7 @@
         <v>20999.0</v>
       </c>
       <c r="G20" s="19">
-        <v>0.004421983575489577</v>
+        <v>0.004467134652201659</v>
       </c>
     </row>
     <row r="21" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21916,7 +21301,7 @@
         <v>12900.0</v>
       </c>
       <c r="G21" s="19">
-        <v>0.006948831332912192</v>
+        <v>0.007019783024888321</v>
       </c>
     </row>
     <row r="22" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21937,7 +21322,7 @@
         <v>14508.0</v>
       </c>
       <c r="G22" s="19">
-        <v>0.005504918328670698</v>
+        <v>0.005561126811924514</v>
       </c>
     </row>
     <row r="23" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21958,7 +21343,7 @@
         <v>23800.0</v>
       </c>
       <c r="G23" s="19">
-        <v>0.002887826008482989</v>
+        <v>0.0029173124259276144</v>
       </c>
     </row>
     <row r="24" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -21979,7 +21364,7 @@
         <v>14300.0</v>
       </c>
       <c r="G24" s="19">
-        <v>0.0047829618265499505</v>
+        <v>0.004831798705442611</v>
       </c>
     </row>
     <row r="25" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22000,7 +21385,7 @@
         <v>9980.0</v>
       </c>
       <c r="G25" s="19">
-        <v>0.006768342207382005</v>
+        <v>0.006837450998267846</v>
       </c>
     </row>
     <row r="26" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22021,7 +21406,7 @@
         <v>17800.0</v>
       </c>
       <c r="G26" s="19">
-        <v>0.0037000270733688295</v>
+        <v>0.0037378065457197556</v>
       </c>
     </row>
     <row r="27" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22042,7 +21427,7 @@
         <v>15600.0</v>
       </c>
       <c r="G27" s="19">
-        <v>0.002526847757422615</v>
+        <v>0.0025526483726866626</v>
       </c>
     </row>
     <row r="28" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22063,7 +21448,7 @@
         <v>11850.0</v>
       </c>
       <c r="G28" s="19">
-        <v>0.0029780705712480825</v>
+        <v>0.003008478439237852</v>
       </c>
     </row>
     <row r="29" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22084,7 +21469,7 @@
         <v>5698.0</v>
       </c>
       <c r="G29" s="19">
-        <v>0.0035195379478386427</v>
+        <v>0.00355547451909928</v>
       </c>
     </row>
     <row r="30" ht="24" customHeight="1" x14ac:dyDescent="0.25">
@@ -22105,109 +21490,88 @@
         <v>14000.0</v>
       </c>
       <c r="G30" s="19">
-        <v>0.000902445627650934</v>
+        <v>0.0009116601331023794</v>
       </c>
     </row>
     <row r="31" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="12" t="inlineStr">
         <is>
-          <t>Roberts Robot</t>
+          <t>Megastar Store</t>
         </is>
       </c>
       <c r="B31" s="13">
-        <v>42</v>
+        <v>16</v>
       </c>
       <c r="C31" s="13">
-        <v>96558</v>
+        <v>95680</v>
       </c>
       <c r="D31" s="13"/>
       <c r="E31" s="13"/>
       <c r="F31" s="13">
-        <v>2299.0</v>
+        <v>5980.0</v>
       </c>
       <c r="G31" s="19">
-        <v>0.003790271636133923</v>
+        <v>0.0014586562129638072</v>
       </c>
     </row>
     <row r="32" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="12" t="inlineStr">
         <is>
-          <t>Megastar Store</t>
+          <t>caolidianpu</t>
         </is>
       </c>
       <c r="B32" s="13">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="C32" s="13">
-        <v>95680</v>
+        <v>75952</v>
       </c>
       <c r="D32" s="13"/>
       <c r="E32" s="13"/>
       <c r="F32" s="13">
-        <v>5980.0</v>
+        <v>9494.0</v>
       </c>
       <c r="G32" s="19">
-        <v>0.0014439130042414945</v>
+        <v>0.0007293281064819036</v>
       </c>
     </row>
     <row r="33" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A33" s="12" t="inlineStr">
         <is>
-          <t>caolidianpu</t>
+          <t>ここclickで他品閲覧可能 安心対応ユウワン商事</t>
         </is>
       </c>
       <c r="B33" s="13">
-        <v>8</v>
+        <v>17</v>
       </c>
       <c r="C33" s="13">
-        <v>75952</v>
+        <v>74188</v>
       </c>
       <c r="D33" s="13"/>
       <c r="E33" s="13"/>
       <c r="F33" s="13">
-        <v>9494.0</v>
+        <v>4364.0</v>
       </c>
       <c r="G33" s="19">
-        <v>0.0007219565021207473</v>
+        <v>0.001549822226274045</v>
       </c>
     </row>
     <row r="34" ht="24" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A34" s="12" t="inlineStr">
         <is>
-          <t>ここclickで他品閲覧可能 安心対応ユウワン商事</t>
+          <t>Unknown</t>
         </is>
       </c>
       <c r="B34" s="13">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="C34" s="13">
-        <v>74188</v>
+        <v>0</v>
       </c>
       <c r="D34" s="13"/>
       <c r="E34" s="13"/>
-      <c r="F34" s="13">
-        <v>4364.0</v>
-      </c>
+      <c r="F34" s="13"/>
       <c r="G34" s="19">
-        <v>0.001534157567006588</v>
-      </c>
-    </row>
-    <row r="35" ht="24" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="12" t="inlineStr">
-        <is>
-          <t>Unknown</t>
-        </is>
-      </c>
-      <c r="B35" s="13">
-        <v>0</v>
-      </c>
-      <c r="C35" s="13">
-        <v>0</v>
-      </c>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
-      <c r="G35" s="19">
         <v>0.0</v>
       </c>
     </row>
